--- a/acc-v3.xlsx
+++ b/acc-v3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="84">
   <si>
     <t>ari</t>
   </si>
@@ -28,18 +28,90 @@
     <t>miou</t>
   </si>
   <si>
+    <t>slate_r_vqvae-clevrtex-42</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>slate_r_vqvae-clevrtex-43</t>
+  </si>
+  <si>
+    <t>std</t>
+  </si>
+  <si>
+    <t>slate_r_vqvae-clevrtex-44</t>
+  </si>
+  <si>
+    <t>slate_r_vqvae-coco-42</t>
+  </si>
+  <si>
+    <t>slate_r_vqvae-coco-43</t>
+  </si>
+  <si>
+    <t>slate_r_vqvae-coco-44</t>
+  </si>
+  <si>
+    <t>slate_r_vqvae-voc-42</t>
+  </si>
+  <si>
+    <t>slate_r_vqvae-voc-43</t>
+  </si>
+  <si>
+    <t>slate_r_vqvae-voc-44</t>
+  </si>
+  <si>
+    <t>steve_c_vqvae-movi_d-42</t>
+  </si>
+  <si>
+    <t>steve_c_vqvae-movi_d-43</t>
+  </si>
+  <si>
+    <t>steve_c_vqvae-movi_d-44</t>
+  </si>
+  <si>
+    <t>vqdino_tfd_r-clevrtex-42</t>
+  </si>
+  <si>
+    <t>vqdino_tfd_r-clevrtex-43</t>
+  </si>
+  <si>
+    <t>vqdino_tfd_r-clevrtex-44</t>
+  </si>
+  <si>
+    <t>vqdino_tfd_r-coco-42</t>
+  </si>
+  <si>
+    <t>vqdino_tfd_r-coco-43</t>
+  </si>
+  <si>
+    <t>vqdino_tfd_r-coco-44</t>
+  </si>
+  <si>
+    <t>vqdino_tfd_r-voc-42</t>
+  </si>
+  <si>
+    <t>vqdino_tfd_r-voc-43</t>
+  </si>
+  <si>
+    <t>vqdino_tfd_r-voc-44</t>
+  </si>
+  <si>
+    <t>vqdino_tfdt_c-movi_d-42</t>
+  </si>
+  <si>
+    <t>vqdino_tfdt_c-movi_d-43</t>
+  </si>
+  <si>
+    <t>vqdino_tfdt_c-movi_d-44</t>
+  </si>
+  <si>
     <t>dinosaur_r-clevrtex-42</t>
   </si>
   <si>
-    <t>mean</t>
-  </si>
-  <si>
     <t>dinosaur_r-clevrtex-43</t>
   </si>
   <si>
-    <t>std</t>
-  </si>
-  <si>
     <t>dinosaur_r-clevrtex-44</t>
   </si>
   <si>
@@ -52,6 +124,114 @@
     <t>dinosaur_r-coco-44</t>
   </si>
   <si>
+    <t>dinosaur_r-voc-42</t>
+  </si>
+  <si>
+    <t>dinosaur_r-voc-43</t>
+  </si>
+  <si>
+    <t>dinosaur_r-voc-44</t>
+  </si>
+  <si>
+    <t>vqdino_mlp_r-clevrtex-42</t>
+  </si>
+  <si>
+    <t>vqdino_mlp_r-clevrtex-43</t>
+  </si>
+  <si>
+    <t>vqdino_mlp_r-clevrtex-44</t>
+  </si>
+  <si>
+    <t>vqdino_mlp_r-coco-42</t>
+  </si>
+  <si>
+    <t>vqdino_mlp_r-coco-43</t>
+  </si>
+  <si>
+    <t>vqdino_mlp_r-coco-44</t>
+  </si>
+  <si>
+    <t>vqdino_mlp_r-voc-42</t>
+  </si>
+  <si>
+    <t>vqdino_mlp_r-voc-43</t>
+  </si>
+  <si>
+    <t>vqdino_mlp_r-voc-44</t>
+  </si>
+  <si>
+    <t>slotdiffusion_r_vqvae-clevrtex-42</t>
+  </si>
+  <si>
+    <t>slotdiffusion_r_vqvae-clevrtex-43</t>
+  </si>
+  <si>
+    <t>slotdiffusion_r_vqvae-clevrtex-44</t>
+  </si>
+  <si>
+    <t>slotdiffusion_r_vqvae-coco-42</t>
+  </si>
+  <si>
+    <t>slotdiffusion_r_vqvae-coco-43</t>
+  </si>
+  <si>
+    <t>slotdiffusion_r_vqvae-coco-44</t>
+  </si>
+  <si>
+    <t>slotdiffusion_r_vqvae-voc-42</t>
+  </si>
+  <si>
+    <t>slotdiffusion_r_vqvae-voc-43</t>
+  </si>
+  <si>
+    <t>slotdiffusion_r_vqvae-voc-44</t>
+  </si>
+  <si>
+    <t>vqdino_dfz_r-clevrtex-42</t>
+  </si>
+  <si>
+    <t>vqdino_dfz_r-clevrtex-43</t>
+  </si>
+  <si>
+    <t>vqdino_dfz_r-clevrtex-44</t>
+  </si>
+  <si>
+    <t>vqdino_dfz_r-coco-42</t>
+  </si>
+  <si>
+    <t>vqdino_dfz_r-coco-43</t>
+  </si>
+  <si>
+    <t>vqdino_dfz_r-coco-44</t>
+  </si>
+  <si>
+    <t>vqdino_dfz_r-voc-42</t>
+  </si>
+  <si>
+    <t>vqdino_dfz_r-voc-43</t>
+  </si>
+  <si>
+    <t>vqdino_dfz_r-voc-44</t>
+  </si>
+  <si>
+    <t>slate_r_vqvae-coco-r384-42</t>
+  </si>
+  <si>
+    <t>slate_r_vqvae-coco-r384-43</t>
+  </si>
+  <si>
+    <t>slate_r_vqvae-coco-r384-44</t>
+  </si>
+  <si>
+    <t>vqdino_tfd_r-coco-r384-42</t>
+  </si>
+  <si>
+    <t>vqdino_tfd_r-coco-r384-43</t>
+  </si>
+  <si>
+    <t>vqdino_tfd_r-coco-r384-44</t>
+  </si>
+  <si>
     <t>dinosaur_r-coco-r384-42</t>
   </si>
   <si>
@@ -61,40 +241,22 @@
     <t>dinosaur_r-coco-r384-44</t>
   </si>
   <si>
-    <t>dinosaur_r-voc-42</t>
-  </si>
-  <si>
-    <t>dinosaur_r-voc-43</t>
-  </si>
-  <si>
-    <t>dinosaur_r-voc-44</t>
-  </si>
-  <si>
-    <t>slate_r_vqvae-clevrtex-42</t>
-  </si>
-  <si>
-    <t>slate_r_vqvae-clevrtex-43</t>
-  </si>
-  <si>
-    <t>slate_r_vqvae-clevrtex-44</t>
-  </si>
-  <si>
-    <t>slate_r_vqvae-coco-42</t>
-  </si>
-  <si>
-    <t>slate_r_vqvae-coco-43</t>
-  </si>
-  <si>
-    <t>slate_r_vqvae-coco-44</t>
-  </si>
-  <si>
-    <t>slate_r_vqvae-coco-r384-42</t>
-  </si>
-  <si>
-    <t>slate_r_vqvae-coco-r384-43</t>
-  </si>
-  <si>
-    <t>slate_r_vqvae-coco-r384-44</t>
+    <t>vqdino_mlp_r-coco-r384-42</t>
+  </si>
+  <si>
+    <t>vqdino_mlp_r-coco-r384-43</t>
+  </si>
+  <si>
+    <t>vqdino_mlp_r-coco-r384-44</t>
+  </si>
+  <si>
+    <t>slotdiffusion_r_vqvae-coco-r384-42</t>
+  </si>
+  <si>
+    <t>slotdiffusion_r_vqvae-coco-r384-43</t>
+  </si>
+  <si>
+    <t>slotdiffusion_r_vqvae-coco-r384-44</t>
   </si>
   <si>
     <t>vqdino_dfz_r-coco-r384-42</t>
@@ -104,168 +266,6 @@
   </si>
   <si>
     <t>vqdino_dfz_r-coco-r384-44</t>
-  </si>
-  <si>
-    <t>vqdino_dfz_r-voc-42</t>
-  </si>
-  <si>
-    <t>vqdino_dfz_r-voc-43</t>
-  </si>
-  <si>
-    <t>vqdino_dfz_r-voc-44</t>
-  </si>
-  <si>
-    <t>vqdino_mlp_r-clevrtex-42</t>
-  </si>
-  <si>
-    <t>vqdino_mlp_r-clevrtex-43</t>
-  </si>
-  <si>
-    <t>vqdino_mlp_r-clevrtex-44</t>
-  </si>
-  <si>
-    <t>vqdino_mlp_r-coco-42</t>
-  </si>
-  <si>
-    <t>vqdino_mlp_r-coco-43</t>
-  </si>
-  <si>
-    <t>vqdino_mlp_r-coco-44</t>
-  </si>
-  <si>
-    <t>vqdino_mlp_r-coco-r384-42</t>
-  </si>
-  <si>
-    <t>vqdino_mlp_r-coco-r384-43</t>
-  </si>
-  <si>
-    <t>vqdino_mlp_r-coco-r384-44</t>
-  </si>
-  <si>
-    <t>vqdino_mlp_r-voc-42</t>
-  </si>
-  <si>
-    <t>vqdino_mlp_r-voc-43</t>
-  </si>
-  <si>
-    <t>vqdino_mlp_r-voc-44</t>
-  </si>
-  <si>
-    <t>vqdino_tfdt_c-movi_d-42</t>
-  </si>
-  <si>
-    <t>vqdino_tfdt_c-movi_d-43</t>
-  </si>
-  <si>
-    <t>vqdino_tfdt_c-movi_d-44</t>
-  </si>
-  <si>
-    <t>vqdino_tfd_r-clevrtex-42</t>
-  </si>
-  <si>
-    <t>vqdino_tfd_r-clevrtex-43</t>
-  </si>
-  <si>
-    <t>vqdino_tfd_r-clevrtex-44</t>
-  </si>
-  <si>
-    <t>vqdino_tfd_r-coco-42</t>
-  </si>
-  <si>
-    <t>vqdino_tfd_r-coco-43</t>
-  </si>
-  <si>
-    <t>vqdino_tfd_r-coco-44</t>
-  </si>
-  <si>
-    <t>vqdino_tfd_r-coco-r384-42</t>
-  </si>
-  <si>
-    <t>vqdino_tfd_r-coco-r384-43</t>
-  </si>
-  <si>
-    <t>vqdino_tfd_r-coco-r384-44</t>
-  </si>
-  <si>
-    <t>vqdino_tfd_r-voc-42</t>
-  </si>
-  <si>
-    <t>vqdino_tfd_r-voc-43</t>
-  </si>
-  <si>
-    <t>vqdino_tfd_r-voc-44</t>
-  </si>
-  <si>
-    <t>slate_r_vqvae-voc-42</t>
-  </si>
-  <si>
-    <t>slate_r_vqvae-voc-43</t>
-  </si>
-  <si>
-    <t>slate_r_vqvae-voc-44</t>
-  </si>
-  <si>
-    <t>slotdiffusion_r_vqvae-clevrtex-42</t>
-  </si>
-  <si>
-    <t>slotdiffusion_r_vqvae-clevrtex-43</t>
-  </si>
-  <si>
-    <t>slotdiffusion_r_vqvae-clevrtex-44</t>
-  </si>
-  <si>
-    <t>slotdiffusion_r_vqvae-coco-42</t>
-  </si>
-  <si>
-    <t>slotdiffusion_r_vqvae-coco-43</t>
-  </si>
-  <si>
-    <t>slotdiffusion_r_vqvae-coco-44</t>
-  </si>
-  <si>
-    <t>slotdiffusion_r_vqvae-coco-r384-42</t>
-  </si>
-  <si>
-    <t>slotdiffusion_r_vqvae-coco-r384-43</t>
-  </si>
-  <si>
-    <t>slotdiffusion_r_vqvae-coco-r384-44</t>
-  </si>
-  <si>
-    <t>slotdiffusion_r_vqvae-voc-42</t>
-  </si>
-  <si>
-    <t>slotdiffusion_r_vqvae-voc-43</t>
-  </si>
-  <si>
-    <t>slotdiffusion_r_vqvae-voc-44</t>
-  </si>
-  <si>
-    <t>steve_c_vqvae-movi_d-42</t>
-  </si>
-  <si>
-    <t>steve_c_vqvae-movi_d-43</t>
-  </si>
-  <si>
-    <t>steve_c_vqvae-movi_d-44</t>
-  </si>
-  <si>
-    <t>vqdino_dfz_r-clevrtex-42</t>
-  </si>
-  <si>
-    <t>vqdino_dfz_r-clevrtex-43</t>
-  </si>
-  <si>
-    <t>vqdino_dfz_r-clevrtex-44</t>
-  </si>
-  <si>
-    <t>vqdino_dfz_r-coco-42</t>
-  </si>
-  <si>
-    <t>vqdino_dfz_r-coco-43</t>
-  </si>
-  <si>
-    <t>vqdino_dfz_r-coco-44</t>
   </si>
 </sst>
 </file>
@@ -274,10 +274,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="0.0_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -288,9 +288,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -304,7 +304,54 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -312,7 +359,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,40 +395,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -380,11 +410,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -395,36 +425,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
@@ -441,7 +441,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -459,19 +489,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -489,13 +507,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -507,7 +519,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -519,7 +585,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -531,37 +603,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,55 +621,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -635,13 +635,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -661,24 +698,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -694,32 +713,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -737,148 +737,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1247,35 +1247,35 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.22043157</v>
+        <v>0.15944238</v>
       </c>
       <c r="C2">
-        <v>0.89681751</v>
+        <v>0.87595671</v>
       </c>
       <c r="D2">
-        <v>0.46029252</v>
+        <v>0.44735795</v>
       </c>
       <c r="E2">
-        <v>0.45428216</v>
+        <v>0.43664154</v>
       </c>
       <c r="G2" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1">
         <f>AVERAGE(B2:B4)*100</f>
-        <v>49.5521843333333</v>
+        <v>17.4379136666667</v>
       </c>
       <c r="I2" s="1">
         <f>AVERAGE(C2:C4)*100</f>
-        <v>89.4214153333333</v>
+        <v>87.362164</v>
       </c>
       <c r="J2" s="1">
         <f>AVERAGE(D2:D4)*100</f>
-        <v>52.1377366666667</v>
+        <v>44.4623963333333</v>
       </c>
       <c r="K2" s="1">
         <f>AVERAGE(E2:E4)*100</f>
-        <v>51.6621806666667</v>
+        <v>43.3211453333333</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1283,35 +1283,35 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.62444514</v>
+        <v>0.15621759</v>
       </c>
       <c r="C3">
-        <v>0.89413249</v>
+        <v>0.85567969</v>
       </c>
       <c r="D3">
-        <v>0.5428921</v>
+        <v>0.42102098</v>
       </c>
       <c r="E3">
-        <v>0.53806084</v>
+        <v>0.40809512</v>
       </c>
       <c r="G3" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="1">
         <f>STDEV(B2:B4)*100</f>
-        <v>23.8391128163239</v>
+        <v>2.87092856110185</v>
       </c>
       <c r="I3" s="1">
         <f>STDEV(C2:C4)*100</f>
-        <v>0.256350074129758</v>
+        <v>1.68958696882078</v>
       </c>
       <c r="J3" s="1">
         <f>STDEV(D2:D4)*100</f>
-        <v>5.36657996861477</v>
+        <v>2.2361691876963</v>
       </c>
       <c r="K3" s="1">
         <f>STDEV(E2:E4)*100</f>
-        <v>5.48576515530672</v>
+        <v>2.35890757464072</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1319,16 +1319,16 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>0.64168882</v>
+        <v>0.20747744</v>
       </c>
       <c r="C4">
-        <v>0.89169246</v>
+        <v>0.88922852</v>
       </c>
       <c r="D4">
-        <v>0.56094748</v>
+        <v>0.46549296</v>
       </c>
       <c r="E4">
-        <v>0.55752242</v>
+        <v>0.4548977</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -1340,32 +1340,35 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>0.21174438</v>
+        <v>0.21033987</v>
       </c>
       <c r="C5">
-        <v>0.35667473</v>
+        <v>0.28870136</v>
       </c>
       <c r="D5">
-        <v>0.28468749</v>
+        <v>0.2763896</v>
       </c>
       <c r="E5">
-        <v>0.27122939</v>
+        <v>0.26275539</v>
+      </c>
+      <c r="G5" t="s">
+        <v>5</v>
       </c>
       <c r="H5" s="1">
         <f>AVERAGE(B5:B7)*100</f>
-        <v>21.1445466666667</v>
+        <v>20.515676</v>
       </c>
       <c r="I5" s="1">
         <f>AVERAGE(C5:C7)*100</f>
-        <v>37.0460956666667</v>
+        <v>28.7975103333333</v>
       </c>
       <c r="J5" s="1">
         <f>AVERAGE(D5:D7)*100</f>
-        <v>28.6554166666667</v>
+        <v>27.4334143333333</v>
       </c>
       <c r="K5" s="1">
         <f>AVERAGE(E5:E7)*100</f>
-        <v>27.3100913333333</v>
+        <v>26.0752526666667</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1373,32 +1376,35 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>0.2208384</v>
+        <v>0.2065455</v>
       </c>
       <c r="C6">
-        <v>0.37595609</v>
+        <v>0.29074591</v>
       </c>
       <c r="D6">
-        <v>0.29176578</v>
+        <v>0.27563325</v>
       </c>
       <c r="E6">
-        <v>0.2783463</v>
+        <v>0.26251724</v>
+      </c>
+      <c r="G6" t="s">
+        <v>7</v>
       </c>
       <c r="H6" s="1">
         <f>STDEV(B5:B7)*100</f>
-        <v>0.954590062789957</v>
+        <v>0.599926830881067</v>
       </c>
       <c r="I6" s="1">
         <f>STDEV(C5:C7)*100</f>
-        <v>1.20207895896623</v>
+        <v>0.319642536963299</v>
       </c>
       <c r="J6" s="1">
         <f>STDEV(D5:D7)*100</f>
-        <v>0.457351050168613</v>
+        <v>0.292964805030116</v>
       </c>
       <c r="K6" s="1">
         <f>STDEV(E5:E7)*100</f>
-        <v>0.46043259366636</v>
+        <v>0.326498917456602</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1406,16 +1412,16 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>0.20175362</v>
+        <v>0.19858491</v>
       </c>
       <c r="C7">
-        <v>0.37875205</v>
+        <v>0.28447804</v>
       </c>
       <c r="D7">
-        <v>0.28320923</v>
+        <v>0.27097958</v>
       </c>
       <c r="E7">
-        <v>0.26972705</v>
+        <v>0.25698495</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -1427,32 +1433,35 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>0.46979541</v>
+        <v>0.22216898</v>
       </c>
       <c r="C8">
-        <v>0.42890996</v>
+        <v>0.25789899</v>
       </c>
       <c r="D8">
-        <v>0.30495346</v>
+        <v>0.37321097</v>
       </c>
       <c r="E8">
-        <v>0.29140419</v>
+        <v>0.36301881</v>
+      </c>
+      <c r="G8" t="s">
+        <v>5</v>
       </c>
       <c r="H8" s="1">
         <f>AVERAGE(B8:B10)*100</f>
-        <v>46.8262923333333</v>
+        <v>22.391769</v>
       </c>
       <c r="I8" s="1">
         <f>AVERAGE(C8:C10)*100</f>
-        <v>42.317932</v>
+        <v>26.2611093333333</v>
       </c>
       <c r="J8" s="1">
         <f>AVERAGE(D8:D10)*100</f>
-        <v>30.3803473333333</v>
+        <v>37.7595803333333</v>
       </c>
       <c r="K8" s="1">
         <f>AVERAGE(E8:E10)*100</f>
-        <v>29.0149173333333</v>
+        <v>36.6282093333333</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1460,32 +1469,35 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>0.46791372</v>
+        <v>0.22534765</v>
       </c>
       <c r="C9">
-        <v>0.42284751</v>
+        <v>0.27204129</v>
       </c>
       <c r="D9">
-        <v>0.30407685</v>
+        <v>0.38001388</v>
       </c>
       <c r="E9">
-        <v>0.29048875</v>
+        <v>0.36892411</v>
+      </c>
+      <c r="G9" t="s">
+        <v>7</v>
       </c>
       <c r="H9" s="1">
         <f>STDEV(B8:B10)*100</f>
-        <v>0.139115380143008</v>
+        <v>0.161312954039657</v>
       </c>
       <c r="I9" s="1">
         <f>STDEV(C8:C10)*100</f>
-        <v>0.557214940819966</v>
+        <v>0.816679042519357</v>
       </c>
       <c r="J9" s="1">
         <f>STDEV(D8:D10)*100</f>
-        <v>0.130827506933113</v>
+        <v>0.380407609761339</v>
       </c>
       <c r="K9" s="1">
         <f>STDEV(E8:E10)*100</f>
-        <v>0.145483797119588</v>
+        <v>0.300126993551619</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1493,16 +1505,16 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>0.46707964</v>
+        <v>0.22423644</v>
       </c>
       <c r="C10">
-        <v>0.41778049</v>
+        <v>0.257893</v>
       </c>
       <c r="D10">
-        <v>0.30238011</v>
+        <v>0.37956256</v>
       </c>
       <c r="E10">
-        <v>0.28855458</v>
+        <v>0.36690336</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1514,32 +1526,35 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>0.25917143</v>
+        <v>0.32484996</v>
       </c>
       <c r="C11">
-        <v>0.36342737</v>
+        <v>0.6644879</v>
       </c>
       <c r="D11">
-        <v>0.41819113</v>
+        <v>0.22756024</v>
       </c>
       <c r="E11">
-        <v>0.40923822</v>
+        <v>0.20885529</v>
+      </c>
+      <c r="G11" t="s">
+        <v>5</v>
       </c>
       <c r="H11" s="1">
         <f>AVERAGE(B11:B13)*100</f>
-        <v>25.6656546666667</v>
+        <v>32.6884903333333</v>
       </c>
       <c r="I11" s="1">
         <f>AVERAGE(C11:C13)*100</f>
-        <v>36.3344323333333</v>
+        <v>66.5421326666667</v>
       </c>
       <c r="J11" s="1">
         <f>AVERAGE(D11:D13)*100</f>
-        <v>41.1548463333333</v>
+        <v>23.047013</v>
       </c>
       <c r="K11" s="1">
         <f>AVERAGE(E11:E13)*100</f>
-        <v>40.2371743333333</v>
+        <v>21.1828466666667</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1547,32 +1562,35 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>0.24971446</v>
+        <v>0.32701793</v>
       </c>
       <c r="C12">
-        <v>0.3769587</v>
+        <v>0.66444218</v>
       </c>
       <c r="D12">
-        <v>0.40773991</v>
+        <v>0.23203583</v>
       </c>
       <c r="E12">
-        <v>0.39755228</v>
+        <v>0.21301356</v>
+      </c>
+      <c r="G12" t="s">
+        <v>7</v>
       </c>
       <c r="H12" s="1">
         <f>STDEV(B11:B13)*100</f>
-        <v>0.608758305169082</v>
+        <v>0.197179835060112</v>
       </c>
       <c r="I12" s="1">
         <f>STDEV(C11:C13)*100</f>
-        <v>1.36560893879483</v>
+        <v>0.165649483733979</v>
       </c>
       <c r="J12" s="1">
         <f>STDEV(D11:D13)*100</f>
-        <v>0.57733134906857</v>
+        <v>0.252247131383094</v>
       </c>
       <c r="K12" s="1">
         <f>STDEV(E11:E13)*100</f>
-        <v>0.610598035626002</v>
+        <v>0.259243782055295</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1580,16 +1598,16 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>0.26108375</v>
+        <v>0.32878682</v>
       </c>
       <c r="C13">
-        <v>0.3496469</v>
+        <v>0.6673339</v>
       </c>
       <c r="D13">
-        <v>0.40871435</v>
+        <v>0.23181432</v>
       </c>
       <c r="E13">
-        <v>0.40032473</v>
+        <v>0.21361655</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1601,32 +1619,35 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>0.15944238</v>
+        <v>0.34458017</v>
       </c>
       <c r="C14">
-        <v>0.87595671</v>
+        <v>0.86181736</v>
       </c>
       <c r="D14">
-        <v>0.44735795</v>
+        <v>0.5162155</v>
       </c>
       <c r="E14">
-        <v>0.43664154</v>
+        <v>0.50770438</v>
+      </c>
+      <c r="G14" t="s">
+        <v>5</v>
       </c>
       <c r="H14" s="1">
         <f>AVERAGE(B14:B16)*100</f>
-        <v>17.4379136666667</v>
+        <v>55.4285743333333</v>
       </c>
       <c r="I14" s="1">
         <f>AVERAGE(C14:C16)*100</f>
-        <v>87.362164</v>
+        <v>85.858035</v>
       </c>
       <c r="J14" s="1">
         <f>AVERAGE(D14:D16)*100</f>
-        <v>44.4623963333333</v>
+        <v>54.3757576666667</v>
       </c>
       <c r="K14" s="1">
         <f>AVERAGE(E14:E16)*100</f>
-        <v>43.3211453333333</v>
+        <v>53.565735</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1634,32 +1655,35 @@
         <v>19</v>
       </c>
       <c r="B15">
-        <v>0.15621759</v>
+        <v>0.6736058</v>
       </c>
       <c r="C15">
-        <v>0.85567969</v>
+        <v>0.8502661</v>
       </c>
       <c r="D15">
-        <v>0.42102098</v>
+        <v>0.56199783</v>
       </c>
       <c r="E15">
-        <v>0.40809512</v>
+        <v>0.55420429</v>
+      </c>
+      <c r="G15" t="s">
+        <v>7</v>
       </c>
       <c r="H15" s="1">
         <f>STDEV(B14:B16)*100</f>
-        <v>2.87092856110185</v>
+        <v>18.2185681425708</v>
       </c>
       <c r="I15" s="1">
         <f>STDEV(C14:C16)*100</f>
-        <v>1.68958696882078</v>
+        <v>0.725890325118744</v>
       </c>
       <c r="J15" s="1">
         <f>STDEV(D14:D16)*100</f>
-        <v>2.2361691876963</v>
+        <v>2.42672283759525</v>
       </c>
       <c r="K15" s="1">
         <f>STDEV(E14:E16)*100</f>
-        <v>2.35890757464072</v>
+        <v>2.46356541981881</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1667,16 +1691,16 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>0.20747744</v>
+        <v>0.64467126</v>
       </c>
       <c r="C16">
-        <v>0.88922852</v>
+        <v>0.86365759</v>
       </c>
       <c r="D16">
-        <v>0.46549296</v>
+        <v>0.5530594</v>
       </c>
       <c r="E16">
-        <v>0.4548977</v>
+        <v>0.54506338</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1688,32 +1712,35 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>0.21033987</v>
+        <v>0.24999255</v>
       </c>
       <c r="C17">
-        <v>0.28870136</v>
+        <v>0.30964002</v>
       </c>
       <c r="D17">
-        <v>0.2763896</v>
+        <v>0.30395016</v>
       </c>
       <c r="E17">
-        <v>0.26275539</v>
+        <v>0.29051259</v>
+      </c>
+      <c r="G17" t="s">
+        <v>5</v>
       </c>
       <c r="H17" s="1">
         <f>AVERAGE(B17:B19)*100</f>
-        <v>20.515676</v>
+        <v>24.3531153333333</v>
       </c>
       <c r="I17" s="1">
         <f>AVERAGE(C17:C19)*100</f>
-        <v>28.7975103333333</v>
+        <v>31.499367</v>
       </c>
       <c r="J17" s="1">
         <f>AVERAGE(D17:D19)*100</f>
-        <v>27.4334143333333</v>
+        <v>30.2356273333333</v>
       </c>
       <c r="K17" s="1">
         <f>AVERAGE(E17:E19)*100</f>
-        <v>26.0752526666667</v>
+        <v>28.8139106666667</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1721,32 +1748,35 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>0.2065455</v>
+        <v>0.22124566</v>
       </c>
       <c r="C18">
-        <v>0.29074591</v>
+        <v>0.32729539</v>
       </c>
       <c r="D18">
-        <v>0.27563325</v>
+        <v>0.29529223</v>
       </c>
       <c r="E18">
-        <v>0.26251724</v>
+        <v>0.27972788</v>
+      </c>
+      <c r="G18" t="s">
+        <v>7</v>
       </c>
       <c r="H18" s="1">
         <f>STDEV(B17:B19)*100</f>
-        <v>0.599926830881067</v>
+        <v>1.98594422795564</v>
       </c>
       <c r="I18" s="1">
         <f>STDEV(C17:C19)*100</f>
-        <v>0.319642536963299</v>
+        <v>1.06833880395173</v>
       </c>
       <c r="J18" s="1">
         <f>STDEV(D17:D19)*100</f>
-        <v>0.292964805030116</v>
+        <v>0.641731240003425</v>
       </c>
       <c r="K18" s="1">
         <f>STDEV(E17:E19)*100</f>
-        <v>0.326498917456602</v>
+        <v>0.751120834922274</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1754,16 +1784,16 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>0.19858491</v>
+        <v>0.25935525</v>
       </c>
       <c r="C19">
-        <v>0.28447804</v>
+        <v>0.3080456</v>
       </c>
       <c r="D19">
-        <v>0.27097958</v>
+        <v>0.30782643</v>
       </c>
       <c r="E19">
-        <v>0.25698495</v>
+        <v>0.29417685</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1775,32 +1805,35 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>0.4230274</v>
+        <v>0.26555267</v>
       </c>
       <c r="C20">
-        <v>0.3443214</v>
+        <v>0.28393701</v>
       </c>
       <c r="D20">
-        <v>0.27635852</v>
+        <v>0.4054099</v>
       </c>
       <c r="E20">
-        <v>0.26079121</v>
+        <v>0.39569238</v>
+      </c>
+      <c r="G20" t="s">
+        <v>5</v>
       </c>
       <c r="H20" s="1">
         <f>AVERAGE(B20:B22)*100</f>
-        <v>43.3764926666667</v>
+        <v>26.8908243333333</v>
       </c>
       <c r="I20" s="1">
         <f>AVERAGE(C20:C22)*100</f>
-        <v>34.0732793333333</v>
+        <v>26.855751</v>
       </c>
       <c r="J20" s="1">
         <f>AVERAGE(D20:D22)*100</f>
-        <v>28.081008</v>
+        <v>40.4891353333333</v>
       </c>
       <c r="K20" s="1">
         <f>AVERAGE(E20:E22)*100</f>
-        <v>26.5909293333333</v>
+        <v>39.5105063333333</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1808,32 +1841,35 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>0.43494594</v>
+        <v>0.26172605</v>
       </c>
       <c r="C21">
-        <v>0.34016693</v>
+        <v>0.26516649</v>
       </c>
       <c r="D21">
-        <v>0.28334823</v>
+        <v>0.40126461</v>
       </c>
       <c r="E21">
-        <v>0.26880878</v>
+        <v>0.39121005</v>
+      </c>
+      <c r="G21" t="s">
+        <v>7</v>
       </c>
       <c r="H21" s="1">
         <f>STDEV(B20:B22)*100</f>
-        <v>1.01984366081539</v>
+        <v>0.932438469267188</v>
       </c>
       <c r="I21" s="1">
         <f>STDEV(C20:C22)*100</f>
-        <v>0.334180163828337</v>
+        <v>1.39955651833143</v>
       </c>
       <c r="J21" s="1">
         <f>STDEV(D20:D22)*100</f>
-        <v>0.386779844900171</v>
+        <v>0.339728158753925</v>
       </c>
       <c r="K21" s="1">
         <f>STDEV(E20:E22)*100</f>
-        <v>0.444544548422691</v>
+        <v>0.363709547389581</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1841,16 +1877,16 @@
         <v>26</v>
       </c>
       <c r="B22">
-        <v>0.44332144</v>
+        <v>0.27944601</v>
       </c>
       <c r="C22">
-        <v>0.33771005</v>
+        <v>0.25656903</v>
       </c>
       <c r="D22">
-        <v>0.28272349</v>
+        <v>0.40799955</v>
       </c>
       <c r="E22">
-        <v>0.26812789</v>
+        <v>0.39841276</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -1862,32 +1898,35 @@
         <v>27</v>
       </c>
       <c r="B23">
-        <v>0.44467548</v>
+        <v>0.37109679</v>
       </c>
       <c r="C23">
-        <v>0.34304851</v>
+        <v>0.74295878</v>
       </c>
       <c r="D23">
-        <v>0.28662109</v>
+        <v>0.2687856</v>
       </c>
       <c r="E23">
-        <v>0.27184302</v>
+        <v>0.25467852</v>
+      </c>
+      <c r="G23" t="s">
+        <v>5</v>
       </c>
       <c r="H23" s="1">
         <f>AVERAGE(B23:B25)*100</f>
-        <v>45.299264</v>
+        <v>36.7388833333333</v>
       </c>
       <c r="I23" s="1">
         <f>AVERAGE(C23:C25)*100</f>
-        <v>34.2588533333333</v>
+        <v>72.4693256666667</v>
       </c>
       <c r="J23" s="1">
         <f>AVERAGE(D23:D25)*100</f>
-        <v>28.9526293333333</v>
+        <v>26.1415843333333</v>
       </c>
       <c r="K23" s="1">
         <f>AVERAGE(E23:E25)*100</f>
-        <v>27.4894506666667</v>
+        <v>24.6128046666667</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1895,32 +1934,35 @@
         <v>28</v>
       </c>
       <c r="B24">
-        <v>0.44743848</v>
+        <v>0.36843684</v>
       </c>
       <c r="C24">
-        <v>0.33827111</v>
+        <v>0.74939191</v>
       </c>
       <c r="D24">
-        <v>0.28488553</v>
+        <v>0.26766258</v>
       </c>
       <c r="E24">
-        <v>0.27001822</v>
+        <v>0.25307843</v>
+      </c>
+      <c r="G24" t="s">
+        <v>7</v>
       </c>
       <c r="H24" s="1">
         <f>STDEV(B23:B25)*100</f>
-        <v>1.2092091678316</v>
+        <v>0.432818945075575</v>
       </c>
       <c r="I24" s="1">
         <f>STDEV(C23:C25)*100</f>
-        <v>0.410680030919855</v>
+        <v>3.7346842542344</v>
       </c>
       <c r="J24" s="1">
         <f>STDEV(D23:D25)*100</f>
-        <v>0.659236314452057</v>
+        <v>1.18055902648971</v>
       </c>
       <c r="K24" s="1">
         <f>STDEV(E23:E25)*100</f>
-        <v>0.692601373652503</v>
+        <v>1.34479548650504</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1928,16 +1970,16 @@
         <v>29</v>
       </c>
       <c r="B25">
-        <v>0.46686396</v>
+        <v>0.36263287</v>
       </c>
       <c r="C25">
-        <v>0.34644598</v>
+        <v>0.68172908</v>
       </c>
       <c r="D25">
-        <v>0.29707226</v>
+        <v>0.24779935</v>
       </c>
       <c r="E25">
-        <v>0.28282228</v>
+        <v>0.23062719</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -1949,32 +1991,35 @@
         <v>30</v>
       </c>
       <c r="B26">
-        <v>0.22313239</v>
+        <v>0.22043157</v>
       </c>
       <c r="C26">
-        <v>0.24033719</v>
+        <v>0.89681751</v>
       </c>
       <c r="D26">
-        <v>0.37249118</v>
+        <v>0.46029252</v>
       </c>
       <c r="E26">
-        <v>0.36082163</v>
+        <v>0.45428216</v>
+      </c>
+      <c r="G26" t="s">
+        <v>5</v>
       </c>
       <c r="H26" s="1">
         <f>AVERAGE(B26:B28)*100</f>
-        <v>22.568694</v>
+        <v>49.5521843333333</v>
       </c>
       <c r="I26" s="1">
         <f>AVERAGE(C26:C28)*100</f>
-        <v>24.3775906666667</v>
+        <v>89.4214153333333</v>
       </c>
       <c r="J26" s="1">
         <f>AVERAGE(D26:D28)*100</f>
-        <v>37.349193</v>
+        <v>52.1377366666667</v>
       </c>
       <c r="K26" s="1">
         <f>AVERAGE(E26:E28)*100</f>
-        <v>36.3096753333333</v>
+        <v>51.6621806666667</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1982,32 +2027,35 @@
         <v>31</v>
       </c>
       <c r="B27">
-        <v>0.22232901</v>
+        <v>0.62444514</v>
       </c>
       <c r="C27">
-        <v>0.24647708</v>
+        <v>0.89413249</v>
       </c>
       <c r="D27">
-        <v>0.37396052</v>
+        <v>0.5428921</v>
       </c>
       <c r="E27">
-        <v>0.36349604</v>
+        <v>0.53806084</v>
+      </c>
+      <c r="G27" t="s">
+        <v>7</v>
       </c>
       <c r="H27" s="1">
         <f>STDEV(B26:B28)*100</f>
-        <v>0.513608992025062</v>
+        <v>23.8391128163239</v>
       </c>
       <c r="I27" s="1">
         <f>STDEV(C26:C28)*100</f>
-        <v>0.313568811099466</v>
+        <v>0.256350074129758</v>
       </c>
       <c r="J27" s="1">
         <f>STDEV(D26:D28)*100</f>
-        <v>0.0867257578865713</v>
+        <v>5.36657996861477</v>
       </c>
       <c r="K27" s="1">
         <f>STDEV(E26:E28)*100</f>
-        <v>0.210408878425634</v>
+        <v>5.48576515530672</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2015,16 +2063,16 @@
         <v>32</v>
       </c>
       <c r="B28">
-        <v>0.23159942</v>
+        <v>0.64168882</v>
       </c>
       <c r="C28">
-        <v>0.24451345</v>
+        <v>0.89169246</v>
       </c>
       <c r="D28">
-        <v>0.37402409</v>
+        <v>0.56094748</v>
       </c>
       <c r="E28">
-        <v>0.36497259</v>
+        <v>0.55752242</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -2036,32 +2084,35 @@
         <v>33</v>
       </c>
       <c r="B29">
-        <v>0.64739817</v>
+        <v>0.21174438</v>
       </c>
       <c r="C29">
-        <v>0.88255185</v>
+        <v>0.35667473</v>
       </c>
       <c r="D29">
-        <v>0.55676335</v>
+        <v>0.28468749</v>
       </c>
       <c r="E29">
-        <v>0.55167902</v>
+        <v>0.27122939</v>
+      </c>
+      <c r="G29" t="s">
+        <v>5</v>
       </c>
       <c r="H29" s="1">
         <f>AVERAGE(B29:B31)*100</f>
-        <v>64.7695363333333</v>
+        <v>21.1445466666667</v>
       </c>
       <c r="I29" s="1">
         <f>AVERAGE(C29:C31)*100</f>
-        <v>88.8258256666667</v>
+        <v>37.0460956666667</v>
       </c>
       <c r="J29" s="1">
         <f>AVERAGE(D29:D31)*100</f>
-        <v>56.083534</v>
+        <v>28.6554166666667</v>
       </c>
       <c r="K29" s="1">
         <f>AVERAGE(E29:E31)*100</f>
-        <v>55.6663036666667</v>
+        <v>27.3100913333333</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2069,32 +2120,35 @@
         <v>34</v>
       </c>
       <c r="B30">
-        <v>0.64494163</v>
+        <v>0.2208384</v>
       </c>
       <c r="C30">
-        <v>0.88804334</v>
+        <v>0.37595609</v>
       </c>
       <c r="D30">
-        <v>0.56041586</v>
+        <v>0.29176578</v>
       </c>
       <c r="E30">
-        <v>0.55648744</v>
+        <v>0.2783463</v>
+      </c>
+      <c r="G30" t="s">
+        <v>7</v>
       </c>
       <c r="H30" s="1">
         <f>STDEV(B29:B31)*100</f>
-        <v>0.291371967370457</v>
+        <v>0.954590062789957</v>
       </c>
       <c r="I30" s="1">
         <f>STDEV(C29:C31)*100</f>
-        <v>0.581684348409282</v>
+        <v>1.20207895896623</v>
       </c>
       <c r="J30" s="1">
         <f>STDEV(D29:D31)*100</f>
-        <v>0.429711349578992</v>
+        <v>0.457351050168613</v>
       </c>
       <c r="K30" s="1">
         <f>STDEV(E29:E31)*100</f>
-        <v>0.507409430699047</v>
+        <v>0.46043259366636</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2102,16 +2156,16 @@
         <v>35</v>
       </c>
       <c r="B31">
-        <v>0.65074629</v>
+        <v>0.20175362</v>
       </c>
       <c r="C31">
-        <v>0.89417958</v>
+        <v>0.37875205</v>
       </c>
       <c r="D31">
-        <v>0.56532681</v>
+        <v>0.28320923</v>
       </c>
       <c r="E31">
-        <v>0.56182265</v>
+        <v>0.26972705</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -2123,32 +2177,35 @@
         <v>36</v>
       </c>
       <c r="B32">
-        <v>0.2251728</v>
+        <v>0.25917143</v>
       </c>
       <c r="C32">
-        <v>0.36501271</v>
+        <v>0.36342737</v>
       </c>
       <c r="D32">
-        <v>0.29377955</v>
+        <v>0.41819113</v>
       </c>
       <c r="E32">
-        <v>0.28070086</v>
+        <v>0.40923822</v>
+      </c>
+      <c r="G32" t="s">
+        <v>5</v>
       </c>
       <c r="H32" s="1">
         <f>AVERAGE(B32:B34)*100</f>
-        <v>22.1499086666667</v>
+        <v>25.6656546666667</v>
       </c>
       <c r="I32" s="1">
         <f>AVERAGE(C32:C34)*100</f>
-        <v>36.000696</v>
+        <v>36.3344323333333</v>
       </c>
       <c r="J32" s="1">
         <f>AVERAGE(D32:D34)*100</f>
-        <v>29.0831476666667</v>
+        <v>41.1548463333333</v>
       </c>
       <c r="K32" s="1">
         <f>AVERAGE(E32:E34)*100</f>
-        <v>27.7878503333333</v>
+        <v>40.2371743333333</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2156,32 +2213,35 @@
         <v>37</v>
       </c>
       <c r="B33">
-        <v>0.21681528</v>
+        <v>0.24971446</v>
       </c>
       <c r="C33">
-        <v>0.3540785</v>
+        <v>0.3769587</v>
       </c>
       <c r="D33">
-        <v>0.28832421</v>
+        <v>0.40773991</v>
       </c>
       <c r="E33">
-        <v>0.27544609</v>
+        <v>0.39755228</v>
+      </c>
+      <c r="G33" t="s">
+        <v>7</v>
       </c>
       <c r="H33" s="1">
         <f>STDEV(B32:B34)*100</f>
-        <v>0.426933853707262</v>
+        <v>0.608758305169082</v>
       </c>
       <c r="I33" s="1">
         <f>STDEV(C32:C34)*100</f>
-        <v>0.552519523538309</v>
+        <v>1.36560893879483</v>
       </c>
       <c r="J33" s="1">
         <f>STDEV(D32:D34)*100</f>
-        <v>0.275425425785879</v>
+        <v>0.57733134906857</v>
       </c>
       <c r="K33" s="1">
         <f>STDEV(E32:E34)*100</f>
-        <v>0.26489986392283</v>
+        <v>0.610598035626002</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2189,16 +2249,16 @@
         <v>38</v>
       </c>
       <c r="B34">
-        <v>0.22250918</v>
+        <v>0.26108375</v>
       </c>
       <c r="C34">
-        <v>0.36092967</v>
+        <v>0.3496469</v>
       </c>
       <c r="D34">
-        <v>0.29039067</v>
+        <v>0.40871435</v>
       </c>
       <c r="E34">
-        <v>0.27748856</v>
+        <v>0.40032473</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -2210,32 +2270,35 @@
         <v>39</v>
       </c>
       <c r="B35">
-        <v>0.47299403</v>
+        <v>0.64739817</v>
       </c>
       <c r="C35">
-        <v>0.42135647</v>
+        <v>0.88255185</v>
       </c>
       <c r="D35">
-        <v>0.30554396</v>
+        <v>0.55676335</v>
       </c>
       <c r="E35">
-        <v>0.29227516</v>
+        <v>0.55167902</v>
+      </c>
+      <c r="G35" t="s">
+        <v>5</v>
       </c>
       <c r="H35" s="1">
         <f>AVERAGE(B35:B37)*100</f>
-        <v>46.546944</v>
+        <v>64.7695363333333</v>
       </c>
       <c r="I35" s="1">
         <f>AVERAGE(C35:C37)*100</f>
-        <v>42.6493286666667</v>
+        <v>88.8258256666667</v>
       </c>
       <c r="J35" s="1">
         <f>AVERAGE(D35:D37)*100</f>
-        <v>30.3042343333333</v>
+        <v>56.083534</v>
       </c>
       <c r="K35" s="1">
         <f>AVERAGE(E35:E37)*100</f>
-        <v>28.9624203333333</v>
+        <v>55.6663036666667</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2243,32 +2306,35 @@
         <v>40</v>
       </c>
       <c r="B36">
-        <v>0.46214628</v>
+        <v>0.64494163</v>
       </c>
       <c r="C36">
-        <v>0.42808789</v>
+        <v>0.88804334</v>
       </c>
       <c r="D36">
-        <v>0.30172026</v>
+        <v>0.56041586</v>
       </c>
       <c r="E36">
-        <v>0.28824311</v>
+        <v>0.55648744</v>
+      </c>
+      <c r="G36" t="s">
+        <v>7</v>
       </c>
       <c r="H36" s="1">
         <f>STDEV(B35:B37)*100</f>
-        <v>0.653126561619568</v>
+        <v>0.291371967370457</v>
       </c>
       <c r="I36" s="1">
         <f>STDEV(C35:C37)*100</f>
-        <v>0.455394996439723</v>
+        <v>0.581684348409282</v>
       </c>
       <c r="J36" s="1">
         <f>STDEV(D35:D37)*100</f>
-        <v>0.216763571335991</v>
+        <v>0.429711349578992</v>
       </c>
       <c r="K36" s="1">
         <f>STDEV(E35:E37)*100</f>
-        <v>0.229646934763634</v>
+        <v>0.507409430699047</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2276,16 +2342,16 @@
         <v>41</v>
       </c>
       <c r="B37">
-        <v>0.46126801</v>
+        <v>0.65074629</v>
       </c>
       <c r="C37">
-        <v>0.4300355</v>
+        <v>0.89417958</v>
       </c>
       <c r="D37">
-        <v>0.30186281</v>
+        <v>0.56532681</v>
       </c>
       <c r="E37">
-        <v>0.28835434</v>
+        <v>0.56182265</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -2297,32 +2363,35 @@
         <v>42</v>
       </c>
       <c r="B38">
-        <v>0.25961101</v>
+        <v>0.2251728</v>
       </c>
       <c r="C38">
-        <v>0.3586618</v>
+        <v>0.36501271</v>
       </c>
       <c r="D38">
-        <v>0.41665635</v>
+        <v>0.29377955</v>
       </c>
       <c r="E38">
-        <v>0.40781781</v>
+        <v>0.28070086</v>
+      </c>
+      <c r="G38" t="s">
+        <v>5</v>
       </c>
       <c r="H38" s="1">
         <f>AVERAGE(B38:B40)*100</f>
-        <v>25.867838</v>
+        <v>22.1499086666667</v>
       </c>
       <c r="I38" s="1">
         <f>AVERAGE(C38:C40)*100</f>
-        <v>35.645025</v>
+        <v>36.000696</v>
       </c>
       <c r="J38" s="1">
         <f>AVERAGE(D38:D40)*100</f>
-        <v>41.4757573333333</v>
+        <v>29.0831476666667</v>
       </c>
       <c r="K38" s="1">
         <f>AVERAGE(E38:E40)*100</f>
-        <v>40.5710013333333</v>
+        <v>27.7878503333333</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2330,32 +2399,35 @@
         <v>43</v>
       </c>
       <c r="B39">
-        <v>0.24946795</v>
+        <v>0.21681528</v>
       </c>
       <c r="C39">
-        <v>0.36401057</v>
+        <v>0.3540785</v>
       </c>
       <c r="D39">
-        <v>0.41317797</v>
+        <v>0.28832421</v>
       </c>
       <c r="E39">
-        <v>0.40415666</v>
+        <v>0.27544609</v>
+      </c>
+      <c r="G39" t="s">
+        <v>7</v>
       </c>
       <c r="H39" s="1">
         <f>STDEV(B38:B40)*100</f>
-        <v>0.878133794879231</v>
+        <v>0.426933853707262</v>
       </c>
       <c r="I39" s="1">
         <f>STDEV(C38:C40)*100</f>
-        <v>0.887521366508433</v>
+        <v>0.552519523538309</v>
       </c>
       <c r="J39" s="1">
         <f>STDEV(D38:D40)*100</f>
-        <v>0.176101833284987</v>
+        <v>0.275425425785879</v>
       </c>
       <c r="K39" s="1">
         <f>STDEV(E38:E40)*100</f>
-        <v>0.189250109327137</v>
+        <v>0.26489986392283</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2363,16 +2435,16 @@
         <v>44</v>
       </c>
       <c r="B40">
-        <v>0.26695618</v>
+        <v>0.22250918</v>
       </c>
       <c r="C40">
-        <v>0.34667838</v>
+        <v>0.36092967</v>
       </c>
       <c r="D40">
-        <v>0.4144384</v>
+        <v>0.29039067</v>
       </c>
       <c r="E40">
-        <v>0.40515557</v>
+        <v>0.27748856</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -2384,32 +2456,35 @@
         <v>45</v>
       </c>
       <c r="B41">
-        <v>0.37109679</v>
+        <v>0.25961101</v>
       </c>
       <c r="C41">
-        <v>0.74295878</v>
+        <v>0.3586618</v>
       </c>
       <c r="D41">
-        <v>0.2687856</v>
+        <v>0.41665635</v>
       </c>
       <c r="E41">
-        <v>0.25467852</v>
+        <v>0.40781781</v>
+      </c>
+      <c r="G41" t="s">
+        <v>5</v>
       </c>
       <c r="H41" s="1">
         <f>AVERAGE(B41:B43)*100</f>
-        <v>36.7388833333333</v>
+        <v>25.867838</v>
       </c>
       <c r="I41" s="1">
         <f>AVERAGE(C41:C43)*100</f>
-        <v>72.4693256666667</v>
+        <v>35.645025</v>
       </c>
       <c r="J41" s="1">
         <f>AVERAGE(D41:D43)*100</f>
-        <v>26.1415843333333</v>
+        <v>41.4757573333333</v>
       </c>
       <c r="K41" s="1">
         <f>AVERAGE(E41:E43)*100</f>
-        <v>24.6128046666667</v>
+        <v>40.5710013333333</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2417,32 +2492,35 @@
         <v>46</v>
       </c>
       <c r="B42">
-        <v>0.36843684</v>
+        <v>0.24946795</v>
       </c>
       <c r="C42">
-        <v>0.74939191</v>
+        <v>0.36401057</v>
       </c>
       <c r="D42">
-        <v>0.26766258</v>
+        <v>0.41317797</v>
       </c>
       <c r="E42">
-        <v>0.25307843</v>
+        <v>0.40415666</v>
+      </c>
+      <c r="G42" t="s">
+        <v>7</v>
       </c>
       <c r="H42" s="1">
         <f>STDEV(B41:B43)*100</f>
-        <v>0.432818945075575</v>
+        <v>0.878133794879231</v>
       </c>
       <c r="I42" s="1">
         <f>STDEV(C41:C43)*100</f>
-        <v>3.7346842542344</v>
+        <v>0.887521366508433</v>
       </c>
       <c r="J42" s="1">
         <f>STDEV(D41:D43)*100</f>
-        <v>1.18055902648971</v>
+        <v>0.176101833284987</v>
       </c>
       <c r="K42" s="1">
         <f>STDEV(E41:E43)*100</f>
-        <v>1.34479548650504</v>
+        <v>0.189250109327137</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2450,16 +2528,16 @@
         <v>47</v>
       </c>
       <c r="B43">
-        <v>0.36263287</v>
+        <v>0.26695618</v>
       </c>
       <c r="C43">
-        <v>0.68172908</v>
+        <v>0.34667838</v>
       </c>
       <c r="D43">
-        <v>0.24779935</v>
+        <v>0.4144384</v>
       </c>
       <c r="E43">
-        <v>0.23062719</v>
+        <v>0.40515557</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -2471,32 +2549,35 @@
         <v>48</v>
       </c>
       <c r="B44">
-        <v>0.34458017</v>
+        <v>0.65520674</v>
       </c>
       <c r="C44">
-        <v>0.86181736</v>
+        <v>0.82916486</v>
       </c>
       <c r="D44">
-        <v>0.5162155</v>
+        <v>0.5473125</v>
       </c>
       <c r="E44">
-        <v>0.50770438</v>
+        <v>0.53982264</v>
+      </c>
+      <c r="G44" t="s">
+        <v>5</v>
       </c>
       <c r="H44" s="1">
         <f>AVERAGE(B44:B46)*100</f>
-        <v>55.4285743333333</v>
+        <v>66.1445496666667</v>
       </c>
       <c r="I44" s="1">
         <f>AVERAGE(C44:C46)*100</f>
-        <v>85.858035</v>
+        <v>82.6757606666667</v>
       </c>
       <c r="J44" s="1">
         <f>AVERAGE(D44:D46)*100</f>
-        <v>54.3757576666667</v>
+        <v>54.332765</v>
       </c>
       <c r="K44" s="1">
         <f>AVERAGE(E44:E46)*100</f>
-        <v>53.565735</v>
+        <v>53.3907733333333</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -2504,32 +2585,35 @@
         <v>49</v>
       </c>
       <c r="B45">
-        <v>0.6736058</v>
+        <v>0.65232837</v>
       </c>
       <c r="C45">
-        <v>0.8502661</v>
+        <v>0.84170955</v>
       </c>
       <c r="D45">
-        <v>0.56199783</v>
+        <v>0.54457003</v>
       </c>
       <c r="E45">
-        <v>0.55420429</v>
+        <v>0.53670019</v>
+      </c>
+      <c r="G45" t="s">
+        <v>7</v>
       </c>
       <c r="H45" s="1">
         <f>STDEV(B44:B46)*100</f>
-        <v>18.2185681425708</v>
+        <v>1.33762333328345</v>
       </c>
       <c r="I45" s="1">
         <f>STDEV(C44:C46)*100</f>
-        <v>0.725890325118744</v>
+        <v>1.6289524041022</v>
       </c>
       <c r="J45" s="1">
         <f>STDEV(D44:D46)*100</f>
-        <v>2.42672283759525</v>
+        <v>0.473003546814396</v>
       </c>
       <c r="K45" s="1">
         <f>STDEV(E44:E46)*100</f>
-        <v>2.46356541981881</v>
+        <v>0.770071786683773</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -2537,16 +2621,16 @@
         <v>50</v>
       </c>
       <c r="B46">
-        <v>0.64467126</v>
+        <v>0.67680138</v>
       </c>
       <c r="C46">
-        <v>0.86365759</v>
+        <v>0.80939841</v>
       </c>
       <c r="D46">
-        <v>0.5530594</v>
+        <v>0.53810042</v>
       </c>
       <c r="E46">
-        <v>0.54506338</v>
+        <v>0.52520037</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -2558,32 +2642,35 @@
         <v>51</v>
       </c>
       <c r="B47">
-        <v>0.24999255</v>
+        <v>0.20584749</v>
       </c>
       <c r="C47">
-        <v>0.30964002</v>
+        <v>0.28876042</v>
       </c>
       <c r="D47">
-        <v>0.30395016</v>
+        <v>0.27651283</v>
       </c>
       <c r="E47">
-        <v>0.29051259</v>
+        <v>0.26247066</v>
+      </c>
+      <c r="G47" t="s">
+        <v>5</v>
       </c>
       <c r="H47" s="1">
         <f>AVERAGE(B47:B49)*100</f>
-        <v>24.3531153333333</v>
+        <v>20.613389</v>
       </c>
       <c r="I47" s="1">
         <f>AVERAGE(C47:C49)*100</f>
-        <v>31.499367</v>
+        <v>28.9538846666667</v>
       </c>
       <c r="J47" s="1">
         <f>AVERAGE(D47:D49)*100</f>
-        <v>30.2356273333333</v>
+        <v>27.503273</v>
       </c>
       <c r="K47" s="1">
         <f>AVERAGE(E47:E49)*100</f>
-        <v>28.8139106666667</v>
+        <v>26.1018106666667</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2591,32 +2678,35 @@
         <v>52</v>
       </c>
       <c r="B48">
-        <v>0.22124566</v>
+        <v>0.20070015</v>
       </c>
       <c r="C48">
-        <v>0.32729539</v>
+        <v>0.2912071</v>
       </c>
       <c r="D48">
-        <v>0.29529223</v>
+        <v>0.27049655</v>
       </c>
       <c r="E48">
-        <v>0.27972788</v>
+        <v>0.25659978</v>
+      </c>
+      <c r="G48" t="s">
+        <v>7</v>
       </c>
       <c r="H48" s="1">
         <f>STDEV(B47:B49)*100</f>
-        <v>1.98594422795564</v>
+        <v>0.5582452730082</v>
       </c>
       <c r="I48" s="1">
         <f>STDEV(C47:C49)*100</f>
-        <v>1.06833880395173</v>
+        <v>0.144582307981763</v>
       </c>
       <c r="J48" s="1">
         <f>STDEV(D47:D49)*100</f>
-        <v>0.641731240003425</v>
+        <v>0.400669751596</v>
       </c>
       <c r="K48" s="1">
         <f>STDEV(E47:E49)*100</f>
-        <v>0.751120834922274</v>
+        <v>0.390047004758829</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -2624,16 +2714,16 @@
         <v>53</v>
       </c>
       <c r="B49">
-        <v>0.25935525</v>
+        <v>0.21185403</v>
       </c>
       <c r="C49">
-        <v>0.3080456</v>
+        <v>0.28864902</v>
       </c>
       <c r="D49">
-        <v>0.30782643</v>
+        <v>0.27808881</v>
       </c>
       <c r="E49">
-        <v>0.29417685</v>
+        <v>0.26398388</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -2645,32 +2735,35 @@
         <v>54</v>
       </c>
       <c r="B50">
-        <v>0.45461315</v>
+        <v>0.19298324</v>
       </c>
       <c r="C50">
-        <v>0.38741681</v>
+        <v>0.21102177</v>
       </c>
       <c r="D50">
-        <v>0.29943082</v>
+        <v>0.35463998</v>
       </c>
       <c r="E50">
-        <v>0.28309727</v>
+        <v>0.34142113</v>
+      </c>
+      <c r="G50" t="s">
+        <v>5</v>
       </c>
       <c r="H50" s="1">
         <f>AVERAGE(B50:B52)*100</f>
-        <v>46.2423353333333</v>
+        <v>20.273278</v>
       </c>
       <c r="I50" s="1">
         <f>AVERAGE(C50:C52)*100</f>
-        <v>37.545417</v>
+        <v>21.64752</v>
       </c>
       <c r="J50" s="1">
         <f>AVERAGE(D50:D52)*100</f>
-        <v>30.3152503333333</v>
+        <v>35.609275</v>
       </c>
       <c r="K50" s="1">
         <f>AVERAGE(E50:E52)*100</f>
-        <v>28.7206203333333</v>
+        <v>34.39761</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -2678,32 +2771,35 @@
         <v>55</v>
       </c>
       <c r="B51">
-        <v>0.46273759</v>
+        <v>0.21855035</v>
       </c>
       <c r="C51">
-        <v>0.36598057</v>
+        <v>0.23811284</v>
       </c>
       <c r="D51">
-        <v>0.30205861</v>
+        <v>0.36709657</v>
       </c>
       <c r="E51">
-        <v>0.2861996</v>
+        <v>0.35571471</v>
+      </c>
+      <c r="G51" t="s">
+        <v>7</v>
       </c>
       <c r="H51" s="1">
         <f>STDEV(B50:B52)*100</f>
-        <v>0.765792194588277</v>
+        <v>1.38215418640143</v>
       </c>
       <c r="I51" s="1">
         <f>STDEV(C50:C52)*100</f>
-        <v>1.09327300536325</v>
+        <v>1.94917420573252</v>
       </c>
       <c r="J51" s="1">
         <f>STDEV(D50:D52)*100</f>
-        <v>0.437248831278407</v>
+        <v>1.03541574106201</v>
       </c>
       <c r="K51" s="1">
         <f>STDEV(E50:E52)*100</f>
-        <v>0.469389490702905</v>
+        <v>1.0692569384451</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2711,16 +2807,16 @@
         <v>56</v>
       </c>
       <c r="B52">
-        <v>0.46991932</v>
+        <v>0.19666475</v>
       </c>
       <c r="C52">
-        <v>0.37296513</v>
+        <v>0.20029099</v>
       </c>
       <c r="D52">
-        <v>0.30796808</v>
+        <v>0.3465417</v>
       </c>
       <c r="E52">
-        <v>0.29232174</v>
+        <v>0.33479246</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -2732,32 +2828,35 @@
         <v>57</v>
       </c>
       <c r="B53">
-        <v>0.26555267</v>
+        <v>0.72406292</v>
       </c>
       <c r="C53">
-        <v>0.28393701</v>
+        <v>0.8260498</v>
       </c>
       <c r="D53">
-        <v>0.4054099</v>
+        <v>0.58267128</v>
       </c>
       <c r="E53">
-        <v>0.39569238</v>
+        <v>0.57541162</v>
+      </c>
+      <c r="G53" t="s">
+        <v>5</v>
       </c>
       <c r="H53" s="1">
         <f>AVERAGE(B53:B55)*100</f>
-        <v>26.8908243333333</v>
+        <v>72.1789936666667</v>
       </c>
       <c r="I53" s="1">
         <f>AVERAGE(C53:C55)*100</f>
-        <v>26.855751</v>
+        <v>81.9293736666667</v>
       </c>
       <c r="J53" s="1">
         <f>AVERAGE(D53:D55)*100</f>
-        <v>40.4891353333333</v>
+        <v>57.6370156666667</v>
       </c>
       <c r="K53" s="1">
         <f>AVERAGE(E53:E55)*100</f>
-        <v>39.5105063333333</v>
+        <v>56.7847746666667</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2765,32 +2864,35 @@
         <v>58</v>
       </c>
       <c r="B54">
-        <v>0.26172605</v>
+        <v>0.71927977</v>
       </c>
       <c r="C54">
-        <v>0.26516649</v>
+        <v>0.79712117</v>
       </c>
       <c r="D54">
-        <v>0.40126461</v>
+        <v>0.56898117</v>
       </c>
       <c r="E54">
-        <v>0.39121005</v>
+        <v>0.55977654</v>
+      </c>
+      <c r="G54" t="s">
+        <v>7</v>
       </c>
       <c r="H54" s="1">
         <f>STDEV(B53:B55)*100</f>
-        <v>0.932438469267188</v>
+        <v>0.240037974721366</v>
       </c>
       <c r="I54" s="1">
         <f>STDEV(C53:C55)*100</f>
-        <v>1.39955651833143</v>
+        <v>1.96842027953695</v>
       </c>
       <c r="J54" s="1">
         <f>STDEV(D53:D55)*100</f>
-        <v>0.339728158753925</v>
+        <v>0.69095848592396</v>
       </c>
       <c r="K54" s="1">
         <f>STDEV(E53:E55)*100</f>
-        <v>0.363709547389581</v>
+        <v>0.782987688185028</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -2798,16 +2900,16 @@
         <v>59</v>
       </c>
       <c r="B55">
-        <v>0.27944601</v>
+        <v>0.72202712</v>
       </c>
       <c r="C55">
-        <v>0.25656903</v>
+        <v>0.83471024</v>
       </c>
       <c r="D55">
-        <v>0.40799955</v>
+        <v>0.57745802</v>
       </c>
       <c r="E55">
-        <v>0.39841276</v>
+        <v>0.56835508</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -2819,32 +2921,35 @@
         <v>60</v>
       </c>
       <c r="B56">
-        <v>0.22216898</v>
+        <v>0.21467201</v>
       </c>
       <c r="C56">
-        <v>0.25789899</v>
+        <v>0.28272805</v>
       </c>
       <c r="D56">
-        <v>0.37321097</v>
+        <v>0.27662274</v>
       </c>
       <c r="E56">
-        <v>0.36301881</v>
+        <v>0.26317972</v>
+      </c>
+      <c r="G56" t="s">
+        <v>5</v>
       </c>
       <c r="H56" s="1">
         <f>AVERAGE(B56:B58)*100</f>
-        <v>22.391769</v>
+        <v>21.155834</v>
       </c>
       <c r="I56" s="1">
         <f>AVERAGE(C56:C58)*100</f>
-        <v>26.2611093333333</v>
+        <v>28.6650946666667</v>
       </c>
       <c r="J56" s="1">
         <f>AVERAGE(D56:D58)*100</f>
-        <v>37.7595803333333</v>
+        <v>27.7361293333333</v>
       </c>
       <c r="K56" s="1">
         <f>AVERAGE(E56:E58)*100</f>
-        <v>36.6282093333333</v>
+        <v>26.398065</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -2852,32 +2957,35 @@
         <v>61</v>
       </c>
       <c r="B57">
-        <v>0.22534765</v>
+        <v>0.21124798</v>
       </c>
       <c r="C57">
-        <v>0.27204129</v>
+        <v>0.27881545</v>
       </c>
       <c r="D57">
-        <v>0.38001388</v>
+        <v>0.27640644</v>
       </c>
       <c r="E57">
-        <v>0.36892411</v>
+        <v>0.26315764</v>
+      </c>
+      <c r="G57" t="s">
+        <v>7</v>
       </c>
       <c r="H57" s="1">
         <f>STDEV(B56:B58)*100</f>
-        <v>0.161312954039657</v>
+        <v>0.297067426307563</v>
       </c>
       <c r="I57" s="1">
         <f>STDEV(C56:C58)*100</f>
-        <v>0.816679042519357</v>
+        <v>1.03692801112726</v>
       </c>
       <c r="J57" s="1">
         <f>STDEV(D56:D58)*100</f>
-        <v>0.380407609761339</v>
+        <v>0.147051556487286</v>
       </c>
       <c r="K57" s="1">
         <f>STDEV(E56:E58)*100</f>
-        <v>0.300126993551619</v>
+        <v>0.140641662543499</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -2885,16 +2993,16 @@
         <v>62</v>
       </c>
       <c r="B58">
-        <v>0.22423644</v>
+        <v>0.20875503</v>
       </c>
       <c r="C58">
-        <v>0.257893</v>
+        <v>0.29840934</v>
       </c>
       <c r="D58">
-        <v>0.37956256</v>
+        <v>0.2790547</v>
       </c>
       <c r="E58">
-        <v>0.36690336</v>
+        <v>0.26560459</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -2906,32 +3014,35 @@
         <v>63</v>
       </c>
       <c r="B59">
-        <v>0.65520674</v>
+        <v>0.22313239</v>
       </c>
       <c r="C59">
-        <v>0.82916486</v>
+        <v>0.24033719</v>
       </c>
       <c r="D59">
-        <v>0.5473125</v>
+        <v>0.37249118</v>
       </c>
       <c r="E59">
-        <v>0.53982264</v>
+        <v>0.36082163</v>
+      </c>
+      <c r="G59" t="s">
+        <v>5</v>
       </c>
       <c r="H59" s="1">
         <f>AVERAGE(B59:B61)*100</f>
-        <v>66.1445496666667</v>
+        <v>22.568694</v>
       </c>
       <c r="I59" s="1">
         <f>AVERAGE(C59:C61)*100</f>
-        <v>82.6757606666667</v>
+        <v>24.3775906666667</v>
       </c>
       <c r="J59" s="1">
         <f>AVERAGE(D59:D61)*100</f>
-        <v>54.332765</v>
+        <v>37.349193</v>
       </c>
       <c r="K59" s="1">
         <f>AVERAGE(E59:E61)*100</f>
-        <v>53.3907733333333</v>
+        <v>36.3096753333333</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -2939,32 +3050,35 @@
         <v>64</v>
       </c>
       <c r="B60">
-        <v>0.65232837</v>
+        <v>0.22232901</v>
       </c>
       <c r="C60">
-        <v>0.84170955</v>
+        <v>0.24647708</v>
       </c>
       <c r="D60">
-        <v>0.54457003</v>
+        <v>0.37396052</v>
       </c>
       <c r="E60">
-        <v>0.53670019</v>
+        <v>0.36349604</v>
+      </c>
+      <c r="G60" t="s">
+        <v>7</v>
       </c>
       <c r="H60" s="1">
         <f>STDEV(B59:B61)*100</f>
-        <v>1.33762333328345</v>
+        <v>0.513608992025062</v>
       </c>
       <c r="I60" s="1">
         <f>STDEV(C59:C61)*100</f>
-        <v>1.6289524041022</v>
+        <v>0.313568811099466</v>
       </c>
       <c r="J60" s="1">
         <f>STDEV(D59:D61)*100</f>
-        <v>0.473003546814396</v>
+        <v>0.0867257578865713</v>
       </c>
       <c r="K60" s="1">
         <f>STDEV(E59:E61)*100</f>
-        <v>0.770071786683773</v>
+        <v>0.210408878425634</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -2972,16 +3086,16 @@
         <v>65</v>
       </c>
       <c r="B61">
-        <v>0.67680138</v>
+        <v>0.23159942</v>
       </c>
       <c r="C61">
-        <v>0.80939841</v>
+        <v>0.24451345</v>
       </c>
       <c r="D61">
-        <v>0.53810042</v>
+        <v>0.37402409</v>
       </c>
       <c r="E61">
-        <v>0.52520037</v>
+        <v>0.36497259</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -2993,32 +3107,35 @@
         <v>66</v>
       </c>
       <c r="B62">
-        <v>0.20584749</v>
+        <v>0.4230274</v>
       </c>
       <c r="C62">
-        <v>0.28876042</v>
+        <v>0.3443214</v>
       </c>
       <c r="D62">
-        <v>0.27651283</v>
+        <v>0.27635852</v>
       </c>
       <c r="E62">
-        <v>0.26247066</v>
+        <v>0.26079121</v>
+      </c>
+      <c r="G62" t="s">
+        <v>5</v>
       </c>
       <c r="H62" s="1">
         <f>AVERAGE(B62:B64)*100</f>
-        <v>20.613389</v>
+        <v>43.3764926666667</v>
       </c>
       <c r="I62" s="1">
         <f>AVERAGE(C62:C64)*100</f>
-        <v>28.9538846666667</v>
+        <v>34.0732793333333</v>
       </c>
       <c r="J62" s="1">
         <f>AVERAGE(D62:D64)*100</f>
-        <v>27.503273</v>
+        <v>28.081008</v>
       </c>
       <c r="K62" s="1">
         <f>AVERAGE(E62:E64)*100</f>
-        <v>26.1018106666667</v>
+        <v>26.5909293333333</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -3026,32 +3143,35 @@
         <v>67</v>
       </c>
       <c r="B63">
-        <v>0.20070015</v>
+        <v>0.43494594</v>
       </c>
       <c r="C63">
-        <v>0.2912071</v>
+        <v>0.34016693</v>
       </c>
       <c r="D63">
-        <v>0.27049655</v>
+        <v>0.28334823</v>
       </c>
       <c r="E63">
-        <v>0.25659978</v>
+        <v>0.26880878</v>
+      </c>
+      <c r="G63" t="s">
+        <v>7</v>
       </c>
       <c r="H63" s="1">
         <f>STDEV(B62:B64)*100</f>
-        <v>0.5582452730082</v>
+        <v>1.01984366081539</v>
       </c>
       <c r="I63" s="1">
         <f>STDEV(C62:C64)*100</f>
-        <v>0.144582307981763</v>
+        <v>0.334180163828337</v>
       </c>
       <c r="J63" s="1">
         <f>STDEV(D62:D64)*100</f>
-        <v>0.400669751596</v>
+        <v>0.386779844900171</v>
       </c>
       <c r="K63" s="1">
         <f>STDEV(E62:E64)*100</f>
-        <v>0.390047004758829</v>
+        <v>0.444544548422691</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -3059,16 +3179,16 @@
         <v>68</v>
       </c>
       <c r="B64">
-        <v>0.21185403</v>
+        <v>0.44332144</v>
       </c>
       <c r="C64">
-        <v>0.28864902</v>
+        <v>0.33771005</v>
       </c>
       <c r="D64">
-        <v>0.27808881</v>
+        <v>0.28272349</v>
       </c>
       <c r="E64">
-        <v>0.26398388</v>
+        <v>0.26812789</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -3080,32 +3200,35 @@
         <v>69</v>
       </c>
       <c r="B65">
-        <v>0.43802661</v>
+        <v>0.45461315</v>
       </c>
       <c r="C65">
-        <v>0.34547716</v>
+        <v>0.38741681</v>
       </c>
       <c r="D65">
-        <v>0.28531048</v>
+        <v>0.29943082</v>
       </c>
       <c r="E65">
-        <v>0.27041504</v>
+        <v>0.28309727</v>
+      </c>
+      <c r="G65" t="s">
+        <v>5</v>
       </c>
       <c r="H65" s="1">
         <f>AVERAGE(B65:B67)*100</f>
-        <v>43.444701</v>
+        <v>46.2423353333333</v>
       </c>
       <c r="I65" s="1">
         <f>AVERAGE(C65:C67)*100</f>
-        <v>34.4903646666667</v>
+        <v>37.545417</v>
       </c>
       <c r="J65" s="1">
         <f>AVERAGE(D65:D67)*100</f>
-        <v>28.3372966666667</v>
+        <v>30.3152503333333</v>
       </c>
       <c r="K65" s="1">
         <f>AVERAGE(E65:E67)*100</f>
-        <v>26.838427</v>
+        <v>28.7206203333333</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -3113,32 +3236,35 @@
         <v>70</v>
       </c>
       <c r="B66">
-        <v>0.42825752</v>
+        <v>0.46273759</v>
       </c>
       <c r="C66">
-        <v>0.34818992</v>
+        <v>0.36598057</v>
       </c>
       <c r="D66">
-        <v>0.28093871</v>
+        <v>0.30205861</v>
       </c>
       <c r="E66">
-        <v>0.26617301</v>
+        <v>0.2861996</v>
+      </c>
+      <c r="G66" t="s">
+        <v>7</v>
       </c>
       <c r="H66" s="1">
         <f>STDEV(B65:B67)*100</f>
-        <v>0.538213937167183</v>
+        <v>0.765792194588277</v>
       </c>
       <c r="I66" s="1">
         <f>STDEV(C65:C67)*100</f>
-        <v>0.360738569306546</v>
+        <v>1.09327300536325</v>
       </c>
       <c r="J66" s="1">
         <f>STDEV(D65:D67)*100</f>
-        <v>0.222781477857414</v>
+        <v>0.437248831278407</v>
       </c>
       <c r="K66" s="1">
         <f>STDEV(E65:E67)*100</f>
-        <v>0.212676682085743</v>
+        <v>0.469389490702905</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -3146,16 +3272,16 @@
         <v>71</v>
       </c>
       <c r="B67">
-        <v>0.4370569</v>
+        <v>0.46991932</v>
       </c>
       <c r="C67">
-        <v>0.34104386</v>
+        <v>0.37296513</v>
       </c>
       <c r="D67">
-        <v>0.28386971</v>
+        <v>0.30796808</v>
       </c>
       <c r="E67">
-        <v>0.26856476</v>
+        <v>0.29232174</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -3167,32 +3293,35 @@
         <v>72</v>
       </c>
       <c r="B68">
-        <v>0.19298324</v>
+        <v>0.46979541</v>
       </c>
       <c r="C68">
-        <v>0.21102177</v>
+        <v>0.42890996</v>
       </c>
       <c r="D68">
-        <v>0.35463998</v>
+        <v>0.30495346</v>
       </c>
       <c r="E68">
-        <v>0.34142113</v>
+        <v>0.29140419</v>
+      </c>
+      <c r="G68" t="s">
+        <v>5</v>
       </c>
       <c r="H68" s="1">
         <f>AVERAGE(B68:B70)*100</f>
-        <v>20.273278</v>
+        <v>46.8262923333333</v>
       </c>
       <c r="I68" s="1">
         <f>AVERAGE(C68:C70)*100</f>
-        <v>21.64752</v>
+        <v>42.317932</v>
       </c>
       <c r="J68" s="1">
         <f>AVERAGE(D68:D70)*100</f>
-        <v>35.609275</v>
+        <v>30.3803473333333</v>
       </c>
       <c r="K68" s="1">
         <f>AVERAGE(E68:E70)*100</f>
-        <v>34.39761</v>
+        <v>29.0149173333333</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -3200,32 +3329,35 @@
         <v>73</v>
       </c>
       <c r="B69">
-        <v>0.21855035</v>
+        <v>0.46791372</v>
       </c>
       <c r="C69">
-        <v>0.23811284</v>
+        <v>0.42284751</v>
       </c>
       <c r="D69">
-        <v>0.36709657</v>
+        <v>0.30407685</v>
       </c>
       <c r="E69">
-        <v>0.35571471</v>
+        <v>0.29048875</v>
+      </c>
+      <c r="G69" t="s">
+        <v>7</v>
       </c>
       <c r="H69" s="1">
         <f>STDEV(B68:B70)*100</f>
-        <v>1.38215418640143</v>
+        <v>0.139115380143008</v>
       </c>
       <c r="I69" s="1">
         <f>STDEV(C68:C70)*100</f>
-        <v>1.94917420573252</v>
+        <v>0.557214940819966</v>
       </c>
       <c r="J69" s="1">
         <f>STDEV(D68:D70)*100</f>
-        <v>1.03541574106201</v>
+        <v>0.130827506933113</v>
       </c>
       <c r="K69" s="1">
         <f>STDEV(E68:E70)*100</f>
-        <v>1.0692569384451</v>
+        <v>0.145483797119588</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -3233,16 +3365,16 @@
         <v>74</v>
       </c>
       <c r="B70">
-        <v>0.19666475</v>
+        <v>0.46707964</v>
       </c>
       <c r="C70">
-        <v>0.20029099</v>
+        <v>0.41778049</v>
       </c>
       <c r="D70">
-        <v>0.3465417</v>
+        <v>0.30238011</v>
       </c>
       <c r="E70">
-        <v>0.33479246</v>
+        <v>0.28855458</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -3254,32 +3386,35 @@
         <v>75</v>
       </c>
       <c r="B71">
-        <v>0.32484996</v>
+        <v>0.47299403</v>
       </c>
       <c r="C71">
-        <v>0.6644879</v>
+        <v>0.42135647</v>
       </c>
       <c r="D71">
-        <v>0.22756024</v>
+        <v>0.30554396</v>
       </c>
       <c r="E71">
-        <v>0.20885529</v>
+        <v>0.29227516</v>
+      </c>
+      <c r="G71" t="s">
+        <v>5</v>
       </c>
       <c r="H71" s="1">
         <f>AVERAGE(B71:B73)*100</f>
-        <v>32.6884903333333</v>
+        <v>46.546944</v>
       </c>
       <c r="I71" s="1">
         <f>AVERAGE(C71:C73)*100</f>
-        <v>66.5421326666667</v>
+        <v>42.6493286666667</v>
       </c>
       <c r="J71" s="1">
         <f>AVERAGE(D71:D73)*100</f>
-        <v>23.047013</v>
+        <v>30.3042343333333</v>
       </c>
       <c r="K71" s="1">
         <f>AVERAGE(E71:E73)*100</f>
-        <v>21.1828466666667</v>
+        <v>28.9624203333333</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -3287,32 +3422,35 @@
         <v>76</v>
       </c>
       <c r="B72">
-        <v>0.32701793</v>
+        <v>0.46214628</v>
       </c>
       <c r="C72">
-        <v>0.66444218</v>
+        <v>0.42808789</v>
       </c>
       <c r="D72">
-        <v>0.23203583</v>
+        <v>0.30172026</v>
       </c>
       <c r="E72">
-        <v>0.21301356</v>
+        <v>0.28824311</v>
+      </c>
+      <c r="G72" t="s">
+        <v>7</v>
       </c>
       <c r="H72" s="1">
         <f>STDEV(B71:B73)*100</f>
-        <v>0.197179835060112</v>
+        <v>0.653126561619568</v>
       </c>
       <c r="I72" s="1">
         <f>STDEV(C71:C73)*100</f>
-        <v>0.165649483733979</v>
+        <v>0.455394996439723</v>
       </c>
       <c r="J72" s="1">
         <f>STDEV(D71:D73)*100</f>
-        <v>0.252247131383094</v>
+        <v>0.216763571335991</v>
       </c>
       <c r="K72" s="1">
         <f>STDEV(E71:E73)*100</f>
-        <v>0.259243782055295</v>
+        <v>0.229646934763634</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -3320,16 +3458,16 @@
         <v>77</v>
       </c>
       <c r="B73">
-        <v>0.32878682</v>
+        <v>0.46126801</v>
       </c>
       <c r="C73">
-        <v>0.6673339</v>
+        <v>0.4300355</v>
       </c>
       <c r="D73">
-        <v>0.23181432</v>
+        <v>0.30186281</v>
       </c>
       <c r="E73">
-        <v>0.21361655</v>
+        <v>0.28835434</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
@@ -3341,32 +3479,35 @@
         <v>78</v>
       </c>
       <c r="B74">
-        <v>0.72406292</v>
+        <v>0.43802661</v>
       </c>
       <c r="C74">
-        <v>0.8260498</v>
+        <v>0.34547716</v>
       </c>
       <c r="D74">
-        <v>0.58267128</v>
+        <v>0.28531048</v>
       </c>
       <c r="E74">
-        <v>0.57541162</v>
+        <v>0.27041504</v>
+      </c>
+      <c r="G74" t="s">
+        <v>5</v>
       </c>
       <c r="H74" s="1">
         <f>AVERAGE(B74:B76)*100</f>
-        <v>72.1789936666667</v>
+        <v>43.444701</v>
       </c>
       <c r="I74" s="1">
         <f>AVERAGE(C74:C76)*100</f>
-        <v>81.9293736666667</v>
+        <v>34.4903646666667</v>
       </c>
       <c r="J74" s="1">
         <f>AVERAGE(D74:D76)*100</f>
-        <v>57.6370156666667</v>
+        <v>28.3372966666667</v>
       </c>
       <c r="K74" s="1">
         <f>AVERAGE(E74:E76)*100</f>
-        <v>56.7847746666667</v>
+        <v>26.838427</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -3374,32 +3515,35 @@
         <v>79</v>
       </c>
       <c r="B75">
-        <v>0.71927977</v>
+        <v>0.42825752</v>
       </c>
       <c r="C75">
-        <v>0.79712117</v>
+        <v>0.34818992</v>
       </c>
       <c r="D75">
-        <v>0.56898117</v>
+        <v>0.28093871</v>
       </c>
       <c r="E75">
-        <v>0.55977654</v>
+        <v>0.26617301</v>
+      </c>
+      <c r="G75" t="s">
+        <v>7</v>
       </c>
       <c r="H75" s="1">
         <f>STDEV(B74:B76)*100</f>
-        <v>0.240037974721366</v>
+        <v>0.538213937167183</v>
       </c>
       <c r="I75" s="1">
         <f>STDEV(C74:C76)*100</f>
-        <v>1.96842027953695</v>
+        <v>0.360738569306546</v>
       </c>
       <c r="J75" s="1">
         <f>STDEV(D74:D76)*100</f>
-        <v>0.69095848592396</v>
+        <v>0.222781477857414</v>
       </c>
       <c r="K75" s="1">
         <f>STDEV(E74:E76)*100</f>
-        <v>0.782987688185028</v>
+        <v>0.212676682085743</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -3407,16 +3551,16 @@
         <v>80</v>
       </c>
       <c r="B76">
-        <v>0.72202712</v>
+        <v>0.4370569</v>
       </c>
       <c r="C76">
-        <v>0.83471024</v>
+        <v>0.34104386</v>
       </c>
       <c r="D76">
-        <v>0.57745802</v>
+        <v>0.28386971</v>
       </c>
       <c r="E76">
-        <v>0.56835508</v>
+        <v>0.26856476</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -3428,32 +3572,35 @@
         <v>81</v>
       </c>
       <c r="B77">
-        <v>0.21467201</v>
+        <v>0.44467548</v>
       </c>
       <c r="C77">
-        <v>0.28272805</v>
+        <v>0.34304851</v>
       </c>
       <c r="D77">
-        <v>0.27662274</v>
+        <v>0.28662109</v>
       </c>
       <c r="E77">
-        <v>0.26317972</v>
+        <v>0.27184302</v>
+      </c>
+      <c r="G77" t="s">
+        <v>5</v>
       </c>
       <c r="H77" s="1">
         <f>AVERAGE(B77:B79)*100</f>
-        <v>21.155834</v>
+        <v>45.299264</v>
       </c>
       <c r="I77" s="1">
         <f>AVERAGE(C77:C79)*100</f>
-        <v>28.6650946666667</v>
+        <v>34.2588533333333</v>
       </c>
       <c r="J77" s="1">
         <f>AVERAGE(D77:D79)*100</f>
-        <v>27.7361293333333</v>
+        <v>28.9526293333333</v>
       </c>
       <c r="K77" s="1">
         <f>AVERAGE(E77:E79)*100</f>
-        <v>26.398065</v>
+        <v>27.4894506666667</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -3461,32 +3608,35 @@
         <v>82</v>
       </c>
       <c r="B78">
-        <v>0.21124798</v>
+        <v>0.44743848</v>
       </c>
       <c r="C78">
-        <v>0.27881545</v>
+        <v>0.33827111</v>
       </c>
       <c r="D78">
-        <v>0.27640644</v>
+        <v>0.28488553</v>
       </c>
       <c r="E78">
-        <v>0.26315764</v>
+        <v>0.27001822</v>
+      </c>
+      <c r="G78" t="s">
+        <v>7</v>
       </c>
       <c r="H78" s="1">
         <f>STDEV(B77:B79)*100</f>
-        <v>0.297067426307563</v>
+        <v>1.2092091678316</v>
       </c>
       <c r="I78" s="1">
         <f>STDEV(C77:C79)*100</f>
-        <v>1.03692801112726</v>
+        <v>0.410680030919855</v>
       </c>
       <c r="J78" s="1">
         <f>STDEV(D77:D79)*100</f>
-        <v>0.147051556487286</v>
+        <v>0.659236314452057</v>
       </c>
       <c r="K78" s="1">
         <f>STDEV(E77:E79)*100</f>
-        <v>0.140641662543499</v>
+        <v>0.692601373652503</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -3494,16 +3644,16 @@
         <v>83</v>
       </c>
       <c r="B79">
-        <v>0.20875503</v>
+        <v>0.46686396</v>
       </c>
       <c r="C79">
-        <v>0.29840934</v>
+        <v>0.34644598</v>
       </c>
       <c r="D79">
-        <v>0.2790547</v>
+        <v>0.29707226</v>
       </c>
       <c r="E79">
-        <v>0.26560459</v>
+        <v>0.28282228</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>

--- a/acc-v3.xlsx
+++ b/acc-v3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="84">
   <si>
     <t>ari</t>
   </si>
@@ -274,10 +274,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="0.0_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -288,100 +288,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -396,6 +304,27 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -403,8 +332,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -419,12 +365,66 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
@@ -441,25 +441,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -477,7 +465,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -489,139 +621,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,6 +632,45 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -652,8 +691,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -664,21 +705,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -698,32 +724,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -737,148 +737,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1208,15 +1208,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:Q79"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="33.5555555555556" customWidth="1"/>
     <col min="2" max="5" width="11.7777777777778"/>
     <col min="8" max="11" width="12.8888888888889"/>
+    <col min="13" max="13" width="30.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11">
+    <row r="1" spans="2:17">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1241,8 +1242,20 @@
       <c r="K1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="N1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1276,6 +1289,26 @@
       <c r="K2" s="1">
         <f>AVERAGE(E2:E4)*100</f>
         <v>43.3211453333333</v>
+      </c>
+      <c r="M2" t="str">
+        <f>LEFT(A2,LEN(A2)-3)</f>
+        <v>slate_r_vqvae-clevrtex</v>
+      </c>
+      <c r="N2" t="str">
+        <f>TEXT(H2,"0.0")&amp;"±"&amp;TEXT(H3,"0.0")</f>
+        <v>17.4±2.9</v>
+      </c>
+      <c r="O2" t="str">
+        <f>TEXT(I2,"0.0")&amp;"±"&amp;TEXT(I3,"0.0")</f>
+        <v>87.4±1.7</v>
+      </c>
+      <c r="P2" t="str">
+        <f>TEXT(J2,"0.0")&amp;"±"&amp;TEXT(J3,"0.0")</f>
+        <v>44.5±2.2</v>
+      </c>
+      <c r="Q2" t="str">
+        <f>TEXT(K2,"0.0")&amp;"±"&amp;TEXT(K3,"0.0")</f>
+        <v>43.3±2.4</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1335,7 +1368,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1369,6 +1402,26 @@
       <c r="K5" s="1">
         <f>AVERAGE(E5:E7)*100</f>
         <v>26.0752526666667</v>
+      </c>
+      <c r="M5" t="str">
+        <f>LEFT(A5,LEN(A5)-3)</f>
+        <v>slate_r_vqvae-coco</v>
+      </c>
+      <c r="N5" t="str">
+        <f>TEXT(H5,"0.0")&amp;"±"&amp;TEXT(H6,"0.0")</f>
+        <v>20.5±0.6</v>
+      </c>
+      <c r="O5" t="str">
+        <f>TEXT(I5,"0.0")&amp;"±"&amp;TEXT(I6,"0.0")</f>
+        <v>28.8±0.3</v>
+      </c>
+      <c r="P5" t="str">
+        <f>TEXT(J5,"0.0")&amp;"±"&amp;TEXT(J6,"0.0")</f>
+        <v>27.4±0.3</v>
+      </c>
+      <c r="Q5" t="str">
+        <f>TEXT(K5,"0.0")&amp;"±"&amp;TEXT(K6,"0.0")</f>
+        <v>26.1±0.3</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1428,7 +1481,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1462,6 +1515,26 @@
       <c r="K8" s="1">
         <f>AVERAGE(E8:E10)*100</f>
         <v>36.6282093333333</v>
+      </c>
+      <c r="M8" t="str">
+        <f>LEFT(A8,LEN(A8)-3)</f>
+        <v>slate_r_vqvae-voc</v>
+      </c>
+      <c r="N8" t="str">
+        <f>TEXT(H8,"0.0")&amp;"±"&amp;TEXT(H9,"0.0")</f>
+        <v>22.4±0.2</v>
+      </c>
+      <c r="O8" t="str">
+        <f>TEXT(I8,"0.0")&amp;"±"&amp;TEXT(I9,"0.0")</f>
+        <v>26.3±0.8</v>
+      </c>
+      <c r="P8" t="str">
+        <f>TEXT(J8,"0.0")&amp;"±"&amp;TEXT(J9,"0.0")</f>
+        <v>37.8±0.4</v>
+      </c>
+      <c r="Q8" t="str">
+        <f>TEXT(K8,"0.0")&amp;"±"&amp;TEXT(K9,"0.0")</f>
+        <v>36.6±0.3</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1521,7 +1594,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:17">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1555,6 +1628,26 @@
       <c r="K11" s="1">
         <f>AVERAGE(E11:E13)*100</f>
         <v>21.1828466666667</v>
+      </c>
+      <c r="M11" t="str">
+        <f>LEFT(A11,LEN(A11)-3)</f>
+        <v>steve_c_vqvae-movi_d</v>
+      </c>
+      <c r="N11" t="str">
+        <f>TEXT(H11,"0.0")&amp;"±"&amp;TEXT(H12,"0.0")</f>
+        <v>32.7±0.2</v>
+      </c>
+      <c r="O11" t="str">
+        <f>TEXT(I11,"0.0")&amp;"±"&amp;TEXT(I12,"0.0")</f>
+        <v>66.5±0.2</v>
+      </c>
+      <c r="P11" t="str">
+        <f>TEXT(J11,"0.0")&amp;"±"&amp;TEXT(J12,"0.0")</f>
+        <v>23.0±0.3</v>
+      </c>
+      <c r="Q11" t="str">
+        <f>TEXT(K11,"0.0")&amp;"±"&amp;TEXT(K12,"0.0")</f>
+        <v>21.2±0.3</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1614,7 +1707,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:17">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1648,6 +1741,26 @@
       <c r="K14" s="1">
         <f>AVERAGE(E14:E16)*100</f>
         <v>53.565735</v>
+      </c>
+      <c r="M14" t="str">
+        <f>LEFT(A14,LEN(A14)-3)</f>
+        <v>vqdino_tfd_r-clevrtex</v>
+      </c>
+      <c r="N14" t="str">
+        <f>TEXT(H14,"0.0")&amp;"±"&amp;TEXT(H15,"0.0")</f>
+        <v>55.4±18.2</v>
+      </c>
+      <c r="O14" t="str">
+        <f>TEXT(I14,"0.0")&amp;"±"&amp;TEXT(I15,"0.0")</f>
+        <v>85.9±0.7</v>
+      </c>
+      <c r="P14" t="str">
+        <f>TEXT(J14,"0.0")&amp;"±"&amp;TEXT(J15,"0.0")</f>
+        <v>54.4±2.4</v>
+      </c>
+      <c r="Q14" t="str">
+        <f>TEXT(K14,"0.0")&amp;"±"&amp;TEXT(K15,"0.0")</f>
+        <v>53.6±2.5</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1707,7 +1820,7 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:17">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1741,6 +1854,26 @@
       <c r="K17" s="1">
         <f>AVERAGE(E17:E19)*100</f>
         <v>28.8139106666667</v>
+      </c>
+      <c r="M17" t="str">
+        <f>LEFT(A17,LEN(A17)-3)</f>
+        <v>vqdino_tfd_r-coco</v>
+      </c>
+      <c r="N17" t="str">
+        <f>TEXT(H17,"0.0")&amp;"±"&amp;TEXT(H18,"0.0")</f>
+        <v>24.4±2.0</v>
+      </c>
+      <c r="O17" t="str">
+        <f>TEXT(I17,"0.0")&amp;"±"&amp;TEXT(I18,"0.0")</f>
+        <v>31.5±1.1</v>
+      </c>
+      <c r="P17" t="str">
+        <f>TEXT(J17,"0.0")&amp;"±"&amp;TEXT(J18,"0.0")</f>
+        <v>30.2±0.6</v>
+      </c>
+      <c r="Q17" t="str">
+        <f>TEXT(K17,"0.0")&amp;"±"&amp;TEXT(K18,"0.0")</f>
+        <v>28.8±0.8</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1800,7 +1933,7 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:17">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -1834,6 +1967,26 @@
       <c r="K20" s="1">
         <f>AVERAGE(E20:E22)*100</f>
         <v>39.5105063333333</v>
+      </c>
+      <c r="M20" t="str">
+        <f>LEFT(A20,LEN(A20)-3)</f>
+        <v>vqdino_tfd_r-voc</v>
+      </c>
+      <c r="N20" t="str">
+        <f>TEXT(H20,"0.0")&amp;"±"&amp;TEXT(H21,"0.0")</f>
+        <v>26.9±0.9</v>
+      </c>
+      <c r="O20" t="str">
+        <f>TEXT(I20,"0.0")&amp;"±"&amp;TEXT(I21,"0.0")</f>
+        <v>26.9±1.4</v>
+      </c>
+      <c r="P20" t="str">
+        <f>TEXT(J20,"0.0")&amp;"±"&amp;TEXT(J21,"0.0")</f>
+        <v>40.5±0.3</v>
+      </c>
+      <c r="Q20" t="str">
+        <f>TEXT(K20,"0.0")&amp;"±"&amp;TEXT(K21,"0.0")</f>
+        <v>39.5±0.4</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1893,7 +2046,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:17">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1927,6 +2080,26 @@
       <c r="K23" s="1">
         <f>AVERAGE(E23:E25)*100</f>
         <v>24.6128046666667</v>
+      </c>
+      <c r="M23" t="str">
+        <f>LEFT(A23,LEN(A23)-3)</f>
+        <v>vqdino_tfdt_c-movi_d</v>
+      </c>
+      <c r="N23" t="str">
+        <f>TEXT(H23,"0.0")&amp;"±"&amp;TEXT(H24,"0.0")</f>
+        <v>36.7±0.4</v>
+      </c>
+      <c r="O23" t="str">
+        <f>TEXT(I23,"0.0")&amp;"±"&amp;TEXT(I24,"0.0")</f>
+        <v>72.5±3.7</v>
+      </c>
+      <c r="P23" t="str">
+        <f>TEXT(J23,"0.0")&amp;"±"&amp;TEXT(J24,"0.0")</f>
+        <v>26.1±1.2</v>
+      </c>
+      <c r="Q23" t="str">
+        <f>TEXT(K23,"0.0")&amp;"±"&amp;TEXT(K24,"0.0")</f>
+        <v>24.6±1.3</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1986,7 +2159,7 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:17">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -2020,6 +2193,26 @@
       <c r="K26" s="1">
         <f>AVERAGE(E26:E28)*100</f>
         <v>51.6621806666667</v>
+      </c>
+      <c r="M26" t="str">
+        <f>LEFT(A26,LEN(A26)-3)</f>
+        <v>dinosaur_r-clevrtex</v>
+      </c>
+      <c r="N26" t="str">
+        <f>TEXT(H26,"0.0")&amp;"±"&amp;TEXT(H27,"0.0")</f>
+        <v>49.6±23.8</v>
+      </c>
+      <c r="O26" t="str">
+        <f>TEXT(I26,"0.0")&amp;"±"&amp;TEXT(I27,"0.0")</f>
+        <v>89.4±0.3</v>
+      </c>
+      <c r="P26" t="str">
+        <f>TEXT(J26,"0.0")&amp;"±"&amp;TEXT(J27,"0.0")</f>
+        <v>52.1±5.4</v>
+      </c>
+      <c r="Q26" t="str">
+        <f>TEXT(K26,"0.0")&amp;"±"&amp;TEXT(K27,"0.0")</f>
+        <v>51.7±5.5</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2079,7 +2272,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:17">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -2113,6 +2306,26 @@
       <c r="K29" s="1">
         <f>AVERAGE(E29:E31)*100</f>
         <v>27.3100913333333</v>
+      </c>
+      <c r="M29" t="str">
+        <f>LEFT(A29,LEN(A29)-3)</f>
+        <v>dinosaur_r-coco</v>
+      </c>
+      <c r="N29" t="str">
+        <f>TEXT(H29,"0.0")&amp;"±"&amp;TEXT(H30,"0.0")</f>
+        <v>21.1±1.0</v>
+      </c>
+      <c r="O29" t="str">
+        <f>TEXT(I29,"0.0")&amp;"±"&amp;TEXT(I30,"0.0")</f>
+        <v>37.0±1.2</v>
+      </c>
+      <c r="P29" t="str">
+        <f>TEXT(J29,"0.0")&amp;"±"&amp;TEXT(J30,"0.0")</f>
+        <v>28.7±0.5</v>
+      </c>
+      <c r="Q29" t="str">
+        <f>TEXT(K29,"0.0")&amp;"±"&amp;TEXT(K30,"0.0")</f>
+        <v>27.3±0.5</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2172,7 +2385,7 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:17">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -2206,6 +2419,26 @@
       <c r="K32" s="1">
         <f>AVERAGE(E32:E34)*100</f>
         <v>40.2371743333333</v>
+      </c>
+      <c r="M32" t="str">
+        <f>LEFT(A32,LEN(A32)-3)</f>
+        <v>dinosaur_r-voc</v>
+      </c>
+      <c r="N32" t="str">
+        <f>TEXT(H32,"0.0")&amp;"±"&amp;TEXT(H33,"0.0")</f>
+        <v>25.7±0.6</v>
+      </c>
+      <c r="O32" t="str">
+        <f>TEXT(I32,"0.0")&amp;"±"&amp;TEXT(I33,"0.0")</f>
+        <v>36.3±1.4</v>
+      </c>
+      <c r="P32" t="str">
+        <f>TEXT(J32,"0.0")&amp;"±"&amp;TEXT(J33,"0.0")</f>
+        <v>41.2±0.6</v>
+      </c>
+      <c r="Q32" t="str">
+        <f>TEXT(K32,"0.0")&amp;"±"&amp;TEXT(K33,"0.0")</f>
+        <v>40.2±0.6</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2265,7 +2498,7 @@
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:17">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -2299,6 +2532,26 @@
       <c r="K35" s="1">
         <f>AVERAGE(E35:E37)*100</f>
         <v>55.6663036666667</v>
+      </c>
+      <c r="M35" t="str">
+        <f>LEFT(A35,LEN(A35)-3)</f>
+        <v>vqdino_mlp_r-clevrtex</v>
+      </c>
+      <c r="N35" t="str">
+        <f>TEXT(H35,"0.0")&amp;"±"&amp;TEXT(H36,"0.0")</f>
+        <v>64.8±0.3</v>
+      </c>
+      <c r="O35" t="str">
+        <f>TEXT(I35,"0.0")&amp;"±"&amp;TEXT(I36,"0.0")</f>
+        <v>88.8±0.6</v>
+      </c>
+      <c r="P35" t="str">
+        <f>TEXT(J35,"0.0")&amp;"±"&amp;TEXT(J36,"0.0")</f>
+        <v>56.1±0.4</v>
+      </c>
+      <c r="Q35" t="str">
+        <f>TEXT(K35,"0.0")&amp;"±"&amp;TEXT(K36,"0.0")</f>
+        <v>55.7±0.5</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2358,7 +2611,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:17">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -2392,6 +2645,26 @@
       <c r="K38" s="1">
         <f>AVERAGE(E38:E40)*100</f>
         <v>27.7878503333333</v>
+      </c>
+      <c r="M38" t="str">
+        <f>LEFT(A38,LEN(A38)-3)</f>
+        <v>vqdino_mlp_r-coco</v>
+      </c>
+      <c r="N38" t="str">
+        <f>TEXT(H38,"0.0")&amp;"±"&amp;TEXT(H39,"0.0")</f>
+        <v>22.1±0.4</v>
+      </c>
+      <c r="O38" t="str">
+        <f>TEXT(I38,"0.0")&amp;"±"&amp;TEXT(I39,"0.0")</f>
+        <v>36.0±0.6</v>
+      </c>
+      <c r="P38" t="str">
+        <f>TEXT(J38,"0.0")&amp;"±"&amp;TEXT(J39,"0.0")</f>
+        <v>29.1±0.3</v>
+      </c>
+      <c r="Q38" t="str">
+        <f>TEXT(K38,"0.0")&amp;"±"&amp;TEXT(K39,"0.0")</f>
+        <v>27.8±0.3</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2451,7 +2724,7 @@
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:17">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -2485,6 +2758,26 @@
       <c r="K41" s="1">
         <f>AVERAGE(E41:E43)*100</f>
         <v>40.5710013333333</v>
+      </c>
+      <c r="M41" t="str">
+        <f>LEFT(A41,LEN(A41)-3)</f>
+        <v>vqdino_mlp_r-voc</v>
+      </c>
+      <c r="N41" t="str">
+        <f>TEXT(H41,"0.0")&amp;"±"&amp;TEXT(H42,"0.0")</f>
+        <v>25.9±0.9</v>
+      </c>
+      <c r="O41" t="str">
+        <f>TEXT(I41,"0.0")&amp;"±"&amp;TEXT(I42,"0.0")</f>
+        <v>35.6±0.9</v>
+      </c>
+      <c r="P41" t="str">
+        <f>TEXT(J41,"0.0")&amp;"±"&amp;TEXT(J42,"0.0")</f>
+        <v>41.5±0.2</v>
+      </c>
+      <c r="Q41" t="str">
+        <f>TEXT(K41,"0.0")&amp;"±"&amp;TEXT(K42,"0.0")</f>
+        <v>40.6±0.2</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2544,7 +2837,7 @@
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:17">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -2578,6 +2871,26 @@
       <c r="K44" s="1">
         <f>AVERAGE(E44:E46)*100</f>
         <v>53.3907733333333</v>
+      </c>
+      <c r="M44" t="str">
+        <f>LEFT(A44,LEN(A44)-3)</f>
+        <v>slotdiffusion_r_vqvae-clevrtex</v>
+      </c>
+      <c r="N44" t="str">
+        <f>TEXT(H44,"0.0")&amp;"±"&amp;TEXT(H45,"0.0")</f>
+        <v>66.1±1.3</v>
+      </c>
+      <c r="O44" t="str">
+        <f>TEXT(I44,"0.0")&amp;"±"&amp;TEXT(I45,"0.0")</f>
+        <v>82.7±1.6</v>
+      </c>
+      <c r="P44" t="str">
+        <f>TEXT(J44,"0.0")&amp;"±"&amp;TEXT(J45,"0.0")</f>
+        <v>54.3±0.5</v>
+      </c>
+      <c r="Q44" t="str">
+        <f>TEXT(K44,"0.0")&amp;"±"&amp;TEXT(K45,"0.0")</f>
+        <v>53.4±0.8</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -2637,7 +2950,7 @@
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:17">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -2671,6 +2984,26 @@
       <c r="K47" s="1">
         <f>AVERAGE(E47:E49)*100</f>
         <v>26.1018106666667</v>
+      </c>
+      <c r="M47" t="str">
+        <f>LEFT(A47,LEN(A47)-3)</f>
+        <v>slotdiffusion_r_vqvae-coco</v>
+      </c>
+      <c r="N47" t="str">
+        <f>TEXT(H47,"0.0")&amp;"±"&amp;TEXT(H48,"0.0")</f>
+        <v>20.6±0.6</v>
+      </c>
+      <c r="O47" t="str">
+        <f>TEXT(I47,"0.0")&amp;"±"&amp;TEXT(I48,"0.0")</f>
+        <v>29.0±0.1</v>
+      </c>
+      <c r="P47" t="str">
+        <f>TEXT(J47,"0.0")&amp;"±"&amp;TEXT(J48,"0.0")</f>
+        <v>27.5±0.4</v>
+      </c>
+      <c r="Q47" t="str">
+        <f>TEXT(K47,"0.0")&amp;"±"&amp;TEXT(K48,"0.0")</f>
+        <v>26.1±0.4</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2730,7 +3063,7 @@
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:17">
       <c r="A50" t="s">
         <v>54</v>
       </c>
@@ -2764,6 +3097,26 @@
       <c r="K50" s="1">
         <f>AVERAGE(E50:E52)*100</f>
         <v>34.39761</v>
+      </c>
+      <c r="M50" t="str">
+        <f>LEFT(A50,LEN(A50)-3)</f>
+        <v>slotdiffusion_r_vqvae-voc</v>
+      </c>
+      <c r="N50" t="str">
+        <f>TEXT(H50,"0.0")&amp;"±"&amp;TEXT(H51,"0.0")</f>
+        <v>20.3±1.4</v>
+      </c>
+      <c r="O50" t="str">
+        <f>TEXT(I50,"0.0")&amp;"±"&amp;TEXT(I51,"0.0")</f>
+        <v>21.6±1.9</v>
+      </c>
+      <c r="P50" t="str">
+        <f>TEXT(J50,"0.0")&amp;"±"&amp;TEXT(J51,"0.0")</f>
+        <v>35.6±1.0</v>
+      </c>
+      <c r="Q50" t="str">
+        <f>TEXT(K50,"0.0")&amp;"±"&amp;TEXT(K51,"0.0")</f>
+        <v>34.4±1.1</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -2823,7 +3176,7 @@
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:17">
       <c r="A53" t="s">
         <v>57</v>
       </c>
@@ -2857,6 +3210,26 @@
       <c r="K53" s="1">
         <f>AVERAGE(E53:E55)*100</f>
         <v>56.7847746666667</v>
+      </c>
+      <c r="M53" t="str">
+        <f>LEFT(A53,LEN(A53)-3)</f>
+        <v>vqdino_dfz_r-clevrtex</v>
+      </c>
+      <c r="N53" t="str">
+        <f>TEXT(H53,"0.0")&amp;"±"&amp;TEXT(H54,"0.0")</f>
+        <v>72.2±0.2</v>
+      </c>
+      <c r="O53" t="str">
+        <f>TEXT(I53,"0.0")&amp;"±"&amp;TEXT(I54,"0.0")</f>
+        <v>81.9±2.0</v>
+      </c>
+      <c r="P53" t="str">
+        <f>TEXT(J53,"0.0")&amp;"±"&amp;TEXT(J54,"0.0")</f>
+        <v>57.6±0.7</v>
+      </c>
+      <c r="Q53" t="str">
+        <f>TEXT(K53,"0.0")&amp;"±"&amp;TEXT(K54,"0.0")</f>
+        <v>56.8±0.8</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2916,7 +3289,7 @@
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:17">
       <c r="A56" t="s">
         <v>60</v>
       </c>
@@ -2950,6 +3323,26 @@
       <c r="K56" s="1">
         <f>AVERAGE(E56:E58)*100</f>
         <v>26.398065</v>
+      </c>
+      <c r="M56" t="str">
+        <f>LEFT(A56,LEN(A56)-3)</f>
+        <v>vqdino_dfz_r-coco</v>
+      </c>
+      <c r="N56" t="str">
+        <f>TEXT(H56,"0.0")&amp;"±"&amp;TEXT(H57,"0.0")</f>
+        <v>21.2±0.3</v>
+      </c>
+      <c r="O56" t="str">
+        <f>TEXT(I56,"0.0")&amp;"±"&amp;TEXT(I57,"0.0")</f>
+        <v>28.7±1.0</v>
+      </c>
+      <c r="P56" t="str">
+        <f>TEXT(J56,"0.0")&amp;"±"&amp;TEXT(J57,"0.0")</f>
+        <v>27.7±0.1</v>
+      </c>
+      <c r="Q56" t="str">
+        <f>TEXT(K56,"0.0")&amp;"±"&amp;TEXT(K57,"0.0")</f>
+        <v>26.4±0.1</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -3009,7 +3402,7 @@
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:17">
       <c r="A59" t="s">
         <v>63</v>
       </c>
@@ -3043,6 +3436,26 @@
       <c r="K59" s="1">
         <f>AVERAGE(E59:E61)*100</f>
         <v>36.3096753333333</v>
+      </c>
+      <c r="M59" t="str">
+        <f>LEFT(A59,LEN(A59)-3)</f>
+        <v>vqdino_dfz_r-voc</v>
+      </c>
+      <c r="N59" t="str">
+        <f>TEXT(H59,"0.0")&amp;"±"&amp;TEXT(H60,"0.0")</f>
+        <v>22.6±0.5</v>
+      </c>
+      <c r="O59" t="str">
+        <f>TEXT(I59,"0.0")&amp;"±"&amp;TEXT(I60,"0.0")</f>
+        <v>24.4±0.3</v>
+      </c>
+      <c r="P59" t="str">
+        <f>TEXT(J59,"0.0")&amp;"±"&amp;TEXT(J60,"0.0")</f>
+        <v>37.3±0.1</v>
+      </c>
+      <c r="Q59" t="str">
+        <f>TEXT(K59,"0.0")&amp;"±"&amp;TEXT(K60,"0.0")</f>
+        <v>36.3±0.2</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -3102,7 +3515,7 @@
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:17">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -3136,6 +3549,26 @@
       <c r="K62" s="1">
         <f>AVERAGE(E62:E64)*100</f>
         <v>26.5909293333333</v>
+      </c>
+      <c r="M62" t="str">
+        <f>LEFT(A62,LEN(A62)-3)</f>
+        <v>slate_r_vqvae-coco-r384</v>
+      </c>
+      <c r="N62" t="str">
+        <f>TEXT(H62,"0.0")&amp;"±"&amp;TEXT(H63,"0.0")</f>
+        <v>43.4±1.0</v>
+      </c>
+      <c r="O62" t="str">
+        <f>TEXT(I62,"0.0")&amp;"±"&amp;TEXT(I63,"0.0")</f>
+        <v>34.1±0.3</v>
+      </c>
+      <c r="P62" t="str">
+        <f>TEXT(J62,"0.0")&amp;"±"&amp;TEXT(J63,"0.0")</f>
+        <v>28.1±0.4</v>
+      </c>
+      <c r="Q62" t="str">
+        <f>TEXT(K62,"0.0")&amp;"±"&amp;TEXT(K63,"0.0")</f>
+        <v>26.6±0.4</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -3195,7 +3628,7 @@
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:17">
       <c r="A65" t="s">
         <v>69</v>
       </c>
@@ -3229,6 +3662,26 @@
       <c r="K65" s="1">
         <f>AVERAGE(E65:E67)*100</f>
         <v>28.7206203333333</v>
+      </c>
+      <c r="M65" t="str">
+        <f>LEFT(A65,LEN(A65)-3)</f>
+        <v>vqdino_tfd_r-coco-r384</v>
+      </c>
+      <c r="N65" t="str">
+        <f>TEXT(H65,"0.0")&amp;"±"&amp;TEXT(H66,"0.0")</f>
+        <v>46.2±0.8</v>
+      </c>
+      <c r="O65" t="str">
+        <f>TEXT(I65,"0.0")&amp;"±"&amp;TEXT(I66,"0.0")</f>
+        <v>37.5±1.1</v>
+      </c>
+      <c r="P65" t="str">
+        <f>TEXT(J65,"0.0")&amp;"±"&amp;TEXT(J66,"0.0")</f>
+        <v>30.3±0.4</v>
+      </c>
+      <c r="Q65" t="str">
+        <f>TEXT(K65,"0.0")&amp;"±"&amp;TEXT(K66,"0.0")</f>
+        <v>28.7±0.5</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -3288,7 +3741,7 @@
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:17">
       <c r="A68" t="s">
         <v>72</v>
       </c>
@@ -3322,6 +3775,26 @@
       <c r="K68" s="1">
         <f>AVERAGE(E68:E70)*100</f>
         <v>29.0149173333333</v>
+      </c>
+      <c r="M68" t="str">
+        <f>LEFT(A68,LEN(A68)-3)</f>
+        <v>dinosaur_r-coco-r384</v>
+      </c>
+      <c r="N68" t="str">
+        <f>TEXT(H68,"0.0")&amp;"±"&amp;TEXT(H69,"0.0")</f>
+        <v>46.8±0.1</v>
+      </c>
+      <c r="O68" t="str">
+        <f>TEXT(I68,"0.0")&amp;"±"&amp;TEXT(I69,"0.0")</f>
+        <v>42.3±0.6</v>
+      </c>
+      <c r="P68" t="str">
+        <f>TEXT(J68,"0.0")&amp;"±"&amp;TEXT(J69,"0.0")</f>
+        <v>30.4±0.1</v>
+      </c>
+      <c r="Q68" t="str">
+        <f>TEXT(K68,"0.0")&amp;"±"&amp;TEXT(K69,"0.0")</f>
+        <v>29.0±0.1</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -3381,7 +3854,7 @@
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:17">
       <c r="A71" t="s">
         <v>75</v>
       </c>
@@ -3415,6 +3888,26 @@
       <c r="K71" s="1">
         <f>AVERAGE(E71:E73)*100</f>
         <v>28.9624203333333</v>
+      </c>
+      <c r="M71" t="str">
+        <f>LEFT(A71,LEN(A71)-3)</f>
+        <v>vqdino_mlp_r-coco-r384</v>
+      </c>
+      <c r="N71" t="str">
+        <f>TEXT(H71,"0.0")&amp;"±"&amp;TEXT(H72,"0.0")</f>
+        <v>46.5±0.7</v>
+      </c>
+      <c r="O71" t="str">
+        <f>TEXT(I71,"0.0")&amp;"±"&amp;TEXT(I72,"0.0")</f>
+        <v>42.6±0.5</v>
+      </c>
+      <c r="P71" t="str">
+        <f>TEXT(J71,"0.0")&amp;"±"&amp;TEXT(J72,"0.0")</f>
+        <v>30.3±0.2</v>
+      </c>
+      <c r="Q71" t="str">
+        <f>TEXT(K71,"0.0")&amp;"±"&amp;TEXT(K72,"0.0")</f>
+        <v>29.0±0.2</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -3474,7 +3967,7 @@
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:17">
       <c r="A74" t="s">
         <v>78</v>
       </c>
@@ -3508,6 +4001,26 @@
       <c r="K74" s="1">
         <f>AVERAGE(E74:E76)*100</f>
         <v>26.838427</v>
+      </c>
+      <c r="M74" t="str">
+        <f>LEFT(A74,LEN(A74)-3)</f>
+        <v>slotdiffusion_r_vqvae-coco-r384</v>
+      </c>
+      <c r="N74" t="str">
+        <f>TEXT(H74,"0.0")&amp;"±"&amp;TEXT(H75,"0.0")</f>
+        <v>43.4±0.5</v>
+      </c>
+      <c r="O74" t="str">
+        <f>TEXT(I74,"0.0")&amp;"±"&amp;TEXT(I75,"0.0")</f>
+        <v>34.5±0.4</v>
+      </c>
+      <c r="P74" t="str">
+        <f>TEXT(J74,"0.0")&amp;"±"&amp;TEXT(J75,"0.0")</f>
+        <v>28.3±0.2</v>
+      </c>
+      <c r="Q74" t="str">
+        <f>TEXT(K74,"0.0")&amp;"±"&amp;TEXT(K75,"0.0")</f>
+        <v>26.8±0.2</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -3567,7 +4080,7 @@
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:17">
       <c r="A77" t="s">
         <v>81</v>
       </c>
@@ -3601,6 +4114,26 @@
       <c r="K77" s="1">
         <f>AVERAGE(E77:E79)*100</f>
         <v>27.4894506666667</v>
+      </c>
+      <c r="M77" t="str">
+        <f>LEFT(A77,LEN(A77)-3)</f>
+        <v>vqdino_dfz_r-coco-r384</v>
+      </c>
+      <c r="N77" t="str">
+        <f>TEXT(H77,"0.0")&amp;"±"&amp;TEXT(H78,"0.0")</f>
+        <v>45.3±1.2</v>
+      </c>
+      <c r="O77" t="str">
+        <f>TEXT(I77,"0.0")&amp;"±"&amp;TEXT(I78,"0.0")</f>
+        <v>34.3±0.4</v>
+      </c>
+      <c r="P77" t="str">
+        <f>TEXT(J77,"0.0")&amp;"±"&amp;TEXT(J78,"0.0")</f>
+        <v>29.0±0.7</v>
+      </c>
+      <c r="Q77" t="str">
+        <f>TEXT(K77,"0.0")&amp;"±"&amp;TEXT(K78,"0.0")</f>
+        <v>27.5±0.7</v>
       </c>
     </row>
     <row r="78" spans="1:11">
